--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,21 +437,6 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Recipe</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Json Recipe</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Prompt</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Prompt Image Ingredients</t>
         </is>
       </c>
     </row>
@@ -466,26 +451,25 @@
           <t>Pizza Delight 🍕✨
 Ingredients:
 - 2 cups all-purpose flour
-- 1 packet (2 1/4 teaspoons) active dry yeast
-- 1 teaspoon sugar
-- 3/4 cup warm water (110°F)
-- 1 tablespoon olive oil
-- 1 teaspoon salt
-- 1 cup marinara sauce
+- 1 packet (2 ¼ tsp) active dry yeast
+- 1 cup warm water (110°F)
+- 1 tbsp olive oil
+- 1 tsp sugar
+- 1 tsp salt
+- 1 cup pizza sauce
 - 2 cups shredded mozzarella cheese
-- 1/2 cup sliced pepperoni
-- Fresh basil leaves for garnish
+- 1 cup assorted toppings (pepperoni, bell peppers, onions, etc.)
 Instructions:
-1. In a small bowl, dissolve the sugar in warm water and add the yeast. Let it sit for about 5 minutes until frothy.
-2. In a large mixing bowl, combine the flour and salt. Make a well in the center and pour in the yeast mixture and olive oil.
+1. In a small bowl, dissolve the sugar and yeast in warm water. Let it sit for about 5 minutes until frothy.
+2. In a large mixing bowl, combine the flour and salt. Make a well in the center and add the yeast mixture and olive oil.
 3. Mix until a dough forms, then knead on a floured surface for about 5-7 minutes until smooth.
-4. Place the dough in a greased bowl, cover with a cloth, and let it rise in a warm place for 1 hour or until doubled in size.
-5. Preheat the oven to 475°F (245°C). Roll out the dough on a floured surface to your desired thickness.
-6. Transfer the rolled dough to a pizza stone or baking sheet. Spread marinara sauce evenly over the base.
-7. Sprinkle shredded mozzarella cheese generously over the sauce and arrange pepperoni slices on top.
-8. Bake in the preheated oven for 12-15 minutes until the crust is golden and the cheese is bubbly.
-9. Remove from the oven, let it cool for a few minutes, and garnish with fresh basil leaves.
-10. Slice and serve hot!
+4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for 1 hour or until doubled in size.
+5. Preheat your oven to 475°F (245°C).
+6. Roll out the dough on a floured surface to your desired thickness and transfer it to a pizza stone or baking sheet.
+7. Spread the pizza sauce evenly over the dough, leaving a small border for the crust.
+8. Sprinkle the shredded mozzarella cheese over the sauce, then add your chosen toppings.
+9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.
+10. Remove from the oven, let it cool for a few minutes, then slice and serve.
 Prep Time: 15 minutes
 Cook Time: 15 minutes
 Total Time: 1 hour 30 minutes
@@ -495,104 +479,6 @@
 Calories: ~350 per serving</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{
-  "name": "pizza",
-  "summary": "This pizza recipe features a homemade crust topped with marinara sauce, mozzarella cheese, and pepperoni. It's a delicious Italian dish perfect for any occasion.",
-  "servings": "4",
-  "prep_time": "15",
-  "cook_time": "15",
-  "total_time": "90",
-  "calories": "350",
-  "course": "Main Course",
-  "cuisine": "Italian",
-  "keywords": [
-    "pizza",
-    "Italian",
-    "cheese",
-    "pepperoni",
-    "homemade",
-    "dinner"
-  ],
-  "notes": "For a crispier crust, bake on a pizza stone. Calories are per serving.",
-  "ingredients": [
-    {
-      "amount": "2",
-      "unit": "cups",
-      "name": "all-purpose flour"
-    },
-    {
-      "amount": "1",
-      "unit": "packet",
-      "name": "active dry yeast"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "sugar"
-    },
-    {
-      "amount": "¾",
-      "unit": "cup",
-      "name": "warm water"
-    },
-    {
-      "amount": "1",
-      "unit": "tablespoon",
-      "name": "olive oil"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "salt"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "marinara sauce"
-    },
-    {
-      "amount": "2",
-      "unit": "cups",
-      "name": "shredded mozzarella cheese"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "sliced pepperoni"
-    },
-    {
-      "amount": "",
-      "unit": "",
-      "name": "Fresh basil leaves for garnish"
-    }
-  ],
-  "instructions": [
-    "In a small bowl, dissolve the sugar in warm water and add the yeast. Let it sit for about 5 minutes until frothy.",
-    "In a large mixing bowl, combine the flour and salt. Make a well in the center and pour in the yeast mixture and olive oil.",
-    "Mix until a dough forms, then knead on a floured surface for about 5-7 minutes until smooth.",
-    "Place the dough in a greased bowl, cover with a cloth, and let it rise in a warm place for 60 minutes or until doubled in size.",
-    "Preheat the oven to 475°F (245°C). Roll out the dough on a floured surface to your desired thickness.",
-    "Transfer the rolled dough to a pizza stone or baking sheet. Spread marinara sauce evenly over the base.",
-    "Sprinkle shredded mozzarella cheese generously over the sauce and arrange pepperoni slices on top.",
-    "Bake in the preheated oven for 12-15 minutes until the crust is golden and the cheese is bubbly.",
-    "Remove from the oven, let it cool for a few minutes, and garnish with fresh basil leaves.",
-    "Slice and serve hot!"
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of a freshly baked pizza topped with melted mozzarella cheese, pepperoni slices, and fresh basil leaves, served in a clean white ceramic plate, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at food center, slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>flour, yeast, sugar, water, olive oil, salt, marinara sauce, mozzarella cheese, pepperoni, basil leaves, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,44 +439,154 @@
           <t>Recipe</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Generated At</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Json Recipe</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Image Ingredients</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pizza</t>
+          <t>Creamy Garlic Chicken Pasta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pizza Delight 🍕✨
+          <t>Creamy Garlic Chicken Pasta 🍝🧄
 Ingredients:
-- 2 cups all-purpose flour
-- 1 packet (2 ¼ tsp) active dry yeast
-- 1 cup warm water (110°F)
-- 1 tbsp olive oil
-- 1 tsp sugar
-- 1 tsp salt
-- 1 cup pizza sauce
-- 2 cups shredded mozzarella cheese
-- 1 cup assorted toppings (pepperoni, bell peppers, onions, etc.)
+- 8 oz fettuccine pasta
+- 2 tablespoons olive oil
+- 1 lb chicken breast, sliced into strips
+- 4 cloves garlic, minced
+- 1 cup heavy cream
+- 1 cup grated Parmesan cheese
+- Salt and pepper to taste
+- Fresh parsley, chopped (for garnish)
 Instructions:
-1. In a small bowl, dissolve the sugar and yeast in warm water. Let it sit for about 5 minutes until frothy.
-2. In a large mixing bowl, combine the flour and salt. Make a well in the center and add the yeast mixture and olive oil.
-3. Mix until a dough forms, then knead on a floured surface for about 5-7 minutes until smooth.
-4. Place the dough in a greased bowl, cover with a damp cloth, and let it rise in a warm place for 1 hour or until doubled in size.
-5. Preheat your oven to 475°F (245°C).
-6. Roll out the dough on a floured surface to your desired thickness and transfer it to a pizza stone or baking sheet.
-7. Spread the pizza sauce evenly over the dough, leaving a small border for the crust.
-8. Sprinkle the shredded mozzarella cheese over the sauce, then add your chosen toppings.
-9. Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.
-10. Remove from the oven, let it cool for a few minutes, then slice and serve.
-Prep Time: 15 minutes
-Cook Time: 15 minutes
-Total Time: 1 hour 30 minutes
+1. Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.
+2. In a large skillet, heat the olive oil over medium heat. Add the sliced chicken breast and season with salt and pepper.
+3. Cook the chicken for about 5-7 minutes, or until it is golden brown and cooked through. Remove the chicken from the skillet and set aside.
+4. In the same skillet, add the minced garlic and sauté for about 1 minute until fragrant.
+5. Pour in the heavy cream and bring to a simmer. Stir in the Parmesan cheese until melted and the sauce is creamy.
+6. Add the cooked chicken back into the skillet and mix well to coat with the sauce.
+7. Toss the cooked fettuccine pasta into the skillet, combining everything evenly.
+8. Adjust seasoning with salt and pepper as needed.
+9. Serve hot, garnished with fresh parsley.
+Prep Time: 10 minutes
+Cook Time: 20 minutes
+Total Time: 30 minutes
 Course: Main Course
 Cuisine: Italian
 Servings: 4
-Calories: ~350 per serving</t>
+Calories: ~600 per serving</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:23</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Creamy Garlic Chicken Pasta",
+  "summary": "This creamy garlic chicken pasta is a delicious and comforting dish that combines tender chicken, fettuccine, and a rich garlic cream sauce. Perfect for a quick weeknight dinner.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "20",
+  "total_time": "30",
+  "calories": "600",
+  "course": "Main Course",
+  "cuisine": "Italian",
+  "keywords": [
+    "pasta",
+    "chicken",
+    "creamy",
+    "garlic",
+    "Italian",
+    "dinner"
+  ],
+  "notes": "Adjust seasoning to taste for a personalized flavor. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "8",
+      "unit": "oz",
+      "name": "fettuccine pasta"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "olive oil"
+    },
+    {
+      "amount": "1",
+      "unit": "lb",
+      "name": "chicken breast, sliced into strips"
+    },
+    {
+      "amount": "4",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "heavy cream"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "grated Parmesan cheese"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh parsley, chopped (for garnish)"
+    }
+  ],
+  "instructions": [
+    "Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.",
+    "In a large skillet, heat the olive oil over medium heat. Add the sliced chicken breast and season with salt and pepper.",
+    "Cook the chicken for about 5-7 minutes, or until it is golden brown and cooked through. Remove the chicken from the skillet and set aside.",
+    "In the same skillet, add the minced garlic and sauté for about 1 minute until fragrant.",
+    "Pour in the heavy cream and bring to a simmer. Stir in the Parmesan cheese until melted and the sauce is creamy.",
+    "Add the cooked chicken back into the skillet and mix well to coat with the sauce.",
+    "Toss the cooked fettuccine pasta into the skillet, combining everything evenly.",
+    "Adjust seasoning with salt and pepper as needed.",
+    "Serve hot, garnished with fresh parsley."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of creamy garlic chicken pasta served in a clean white ceramic bowl, showcasing the fettuccine coated in a rich sauce, tender chicken strips, and a sprinkle of fresh parsley on top, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>fettuccine pasta, olive oil, chicken breast, garlic, heavy cream, Parmesan cheese, salt, pepper, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
     </row>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:AJ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,91 +459,595 @@
           <t>Prompt Image Ingredients</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>main_image</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>image_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>image_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>image_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>image_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>statu</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>error</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>main_image_ingredients</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>image_ing_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>statu_ing</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>error_ing</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statut Article</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>article_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_article</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_title</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>recipe_title_pin</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_description</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_keywords</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_focus_keyword</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_description</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_pillar_content</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_image</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>post_url</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Creamy Garlic Chicken Pasta</t>
+          <t>Viral Dessert Everyone Is Making Right Now</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Creamy Garlic Chicken Pasta 🍝🧄
+          <t>Viral Dessert Everyone Is Making Right Now 🍰✨
 Ingredients:
-- 8 oz fettuccine pasta
-- 2 tablespoons olive oil
-- 1 lb chicken breast, sliced into strips
-- 4 cloves garlic, minced
+- 1 cup all-purpose flour
+- 1/2 cup granulated sugar
+- 1/4 cup unsweetened cocoa powder
+- 1/2 teaspoon baking powder
+- 1/4 teaspoon salt
+- 3/4 cup milk
+- 1/4 cup vegetable oil
+- 1 teaspoon vanilla extract
+- 1/2 cup chocolate chips
+- 1/2 cup whipped cream for topping
+Instructions:
+1. Preheat your oven to 350°F (175°C) and grease a 9-inch round cake pan.
+2. In a large mixing bowl, combine the flour, sugar, cocoa powder, baking powder, and salt.
+3. In another bowl, whisk together the milk, vegetable oil, and vanilla extract until well combined.
+4. Pour the wet ingredients into the dry ingredients and mix until just combined.
+5. Fold in the chocolate chips gently to avoid overmixing.
+6. Pour the batter into the prepared cake pan and spread evenly.
+7. Bake in the preheated oven for 25-30 minutes or until a toothpick inserted in the center comes out clean.
+8. Allow the cake to cool in the pan for 10 minutes, then transfer it to a wire rack to cool completely.
+9. Once cooled, top with whipped cream and additional chocolate chips if desired.
+10. Slice and serve to enjoy your viral dessert!
+Prep Time: 15 minutes
+Cook Time: 30 minutes
+Total Time: 45 minutes
+Course: Dessert
+Cuisine: American
+Servings: 8
+Calories: ~250 per serving</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:59:07</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Viral Dessert Everyone Is Making Right Now",
+  "summary": "This delicious dessert combines chocolate and whipped cream for a delightful treat. Perfect for sharing with friends and family.",
+  "servings": "8",
+  "prep_time": "15",
+  "cook_time": "30",
+  "total_time": "45",
+  "calories": "250",
+  "course": "Dessert",
+  "cuisine": "American",
+  "keywords": [
+    "chocolate",
+    "cake",
+    "dessert",
+    "whipped cream",
+    "easy recipe"
+  ],
+  "notes": "Top with extra chocolate chips for added flavor. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "all-purpose flour"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "granulated sugar"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "unsweetened cocoa powder"
+    },
+    {
+      "amount": "½",
+      "unit": "teaspoon",
+      "name": "baking powder"
+    },
+    {
+      "amount": "¼",
+      "unit": "teaspoon",
+      "name": "salt"
+    },
+    {
+      "amount": "¾",
+      "unit": "cup",
+      "name": "milk"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "vegetable oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "vanilla extract"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "chocolate chips"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "whipped cream for topping"
+    }
+  ],
+  "instructions": [
+    "Preheat your oven to 350°F (175°C) and grease a 9-inch round cake pan.",
+    "In a large mixing bowl, combine the flour, sugar, cocoa powder, baking powder, and salt.",
+    "In another bowl, whisk together the milk, vegetable oil, and vanilla extract until well combined.",
+    "Pour the wet ingredients into the dry ingredients and mix until just combined.",
+    "Fold in the chocolate chips gently to avoid overmixing.",
+    "Pour the batter into the prepared cake pan and spread evenly.",
+    "Bake in the preheated oven for 25-30 minutes or until a toothpick inserted in the center comes out clean.",
+    "Allow the cake to cool in the pan for 10 minutes, then transfer it to a wire rack to cool completely.",
+    "Once cooled, top with whipped cream and additional chocolate chips if desired.",
+    "Slice and serve to enjoy your viral dessert!"
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a decadent chocolate cake topped with whipped cream and chocolate chips, served in a clean white ceramic plate on a light neutral surface. The texture of the cake is visible, showcasing its moist interior and rich color, with a shallow depth of field and soft natural daylight illuminating the scene. The composition fills 90–100% of the frame, with sharp focus at the center of the cake, captured at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>flour, sugar, cocoa powder, baking powder, salt, milk, vegetable oil, vanilla extract, chocolate chips, whipped cream, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0521001/f5595c88667.png</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/a8ca4d9c61c.png</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/5495419ef1f.png</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/8c2f35701e7.png</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/e0788575df9.png</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0521001/4d5fa1a064b.png</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/c5016f40b10.png</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/cce9eddf70d.png</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/2bae19cfef8.png</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/71fedab8e4b.png</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy Chocolate Cake Recipe for Desserts Everyone Will Love
+## Introduction
+This viral dessert has captured the hearts (and taste buds) of food lovers everywhere. Known for its delightful chocolate flavor and smooth texture, it has quickly become a must-try among dessert enthusiasts. Imagine a rich and indulgent cake that not only satisfies your sweet tooth but also impresses your guests with its luscious chocolate taste. This cake is perfect for any occasion, whether it’s a family gathering, a birthday celebration, or just a sweet evening treat.
+The beauty of this easy chocolate cake lies in its simplicity. With just a handful of ingredients, you can create a dessert that is both satisfying and enticingly delicious. As you slice into the soft, moist layers, your mouth will be greeted by melty pockets of chocolate chips that enhance the overall experience. Topped with fluffy whipped cream, this cake is not just a dessert; it’s a celebration of flavors that will leave everyone asking for more!
+## Recipe Overview
+- Prep Time: 15 minutes  
+- Cook Time: 30 minutes  
+- Total Time: 45 minutes  
+- Course: Dessert  
+- Cuisine: American  
+- Servings: 8  
+- Calories: ~250 per serving  
+This American-style chocolate cake is the perfect blend of simplicity and indulgence, making it an ideal dessert for any occasion. With a preparation time of just 15 minutes and a cooking duration of 30 minutes, you can have this treat ready to serve in under an hour. Not only is it quick to make, but it also yields 8 generous servings, each rich in flavor at only ~250 calories.
+## Ingredients
+### To create this delectable dessert, you'll need the following ingredients:
+- All-purpose flour: 1 cup  
+- Granulated sugar: 1/2 cup  
+- Unsweetened cocoa powder: 1/4 cup  
+- Baking powder: 1/2 teaspoon  
+- Salt: 1/4 teaspoon  
+- Milk: 3/4 cup  
+- Vegetable oil: 1/4 cup  
+- Vanilla extract: 1 teaspoon  
+- Chocolate chips: 1/2 cup  
+- Whipped cream: 1/2 cup for topping
+{{image_ing_1}}
+## Instructions
+1. Preheat your oven to 350°F (175°C) and grease a 9-inch round cake pan.
+2. In a large mixing bowl, combine the flour, sugar, cocoa powder, baking powder, and salt.
+3. In another bowl, whisk together the milk, vegetable oil, and vanilla extract until well combined.
+4. Pour the wet ingredients into the dry ingredients and mix until just combined.
+5. Fold in the chocolate chips gently to avoid overmixing.
+6. Pour the batter into the prepared cake pan and spread evenly.
+7. Bake in the preheated oven for 25-30 minutes or until a toothpick inserted in the center comes out clean.
+8. Allow the cake to cool in the pan for 10 minutes, then transfer it to a wire rack to cool completely.
+9. Once cooled, top with whipped cream and additional chocolate chips if desired.
+10. Slice and serve to enjoy your viral dessert!
+## Preparing Your Kitchen
+### Essential Equipment
+To ensure a smooth baking process, gather the essential equipment needed for this chocolate cake. You will require a 9-inch round cake pan, which is crucial for achieving the desired cake size and texture. Mixing bowls are vital; having a large bowl for the dry ingredients and a medium one for the wet ingredients will keep things organized. A whisk and spatula will help you mix your ingredients thoroughly, while a toothpick will be handy for checking the doneness of your cake. Don’t forget a wire rack for cooling, which allows air to circulate and prevents sogginess on the bottom of the cake.
+### Prepping the Oven
+Before diving into the mixing process, preheat your oven to 350°F (175°C). This will ensure that the cake starts baking at the right temperature for optimal rising and texture. Additionally, greasing the cake pan is essential to prevent any unsightly sticking. Use a little vegetable oil or butter, and if you prefer, a dusting of cocoa powder can be added for an extra layer of protection against sticking.
+## Mixing the Dry Ingredients
+### Flour Mixture
+Starting with your dry ingredients lays the groundwork for your cake’s texture. Measure out 1 cup of all-purpose flour, which will serve as the base. If you want a lighter texture, consider sifting the flour to aerate it, which can lead to a fluffier cake. Separating the flour into a mixing bowl will prepare for the addition of other dry components.
+### Incorporating Cocoa Powder
+Next, sift in 1/4 cup of unsweetened cocoa powder. Choosing high-quality cocoa can make a significant difference in flavor; it adds a rich, deep chocolate experience that is key to this recipe. Cocoa powder not only enhances the flavor but also contributes to the color and richness of your cake. Balancing the sweetness from the sugar with the cocoa's slight bitterness is what makes this cake so appealing.
+### Adding Leavening Agents
+To ensure that your cake rises beautifully, add 1/2 teaspoon of baking powder to the flour and cocoa mixture. This leavening agent creates the airy structure necessary for a light cake. It's worth noting that salt, although often associated with savory dishes, plays an essential role in sweet recipes. By including 1/4 teaspoon of salt, you elevate the overall flavor profile, allowing the sweetness and chocolate notes to shine even brighter.
+## Combining the Wet Ingredients
+### Milk and Oil Mixture
+In a separate medium bowl, it's time to create your wet mixture. Combine 3/4 cup of milk, 1/4 cup of vegetable oil, and 1 teaspoon of vanilla extract. Be sure to use ingredients that are at room temperature for better emulsion and mixing. The milk provides moisture, while the vegetable oil adds richness and tenderness; this combination ensures that your cake will be moist and flavorful.
+### Adding Flavor with Vanilla
+The vanilla extract is not just an ingredient; it’s a flavor enhancer that brings everything together. High-quality vanilla extract can elevate your dessert from good to great. As you whisk the wet ingredients together, the inviting aroma of vanilla will fill your kitchen, making the anticipation of the final product even more delightful. This step is crucial, as it not only blends the liquids but also starts to infuse your cake batter with a warm, comforting flavor that pairs harmoniously with chocolate. 
+Stay tuned for the rest of the article, where we'll delve into the mixing, baking, and presentation steps of this delicious cake!
+### Alternatives to vanilla if you'd like to experiment
+Vanilla extract is a staple in many dessert recipes, providing a warm and sweet undertone that enhances flavor. However, if you're looking to shake things up, several alternatives can add a unique twist to your cake. 
+You might consider almond extract as a substitute for vanilla; it imparts a nutty flavor that pairs wonderfully with chocolate. For a more aromatic profile, try using orange or lemon zest—it adds a refreshing citrus note that can brighten the overall taste. Additionally, coconut extract can provide a tropical flair, making your dessert stand out with a hint of sweetness that complements the chocolate beautifully.
+## Creating the Batter
+### Mixing Techniques
+Achieving the right batter consistency is crucial for a perfect cake. When mixing your dry ingredients, such as flour and cocoa powder, ensure they are well-blended to avoid any clumps. Use a whisk to integrate these dry components thoroughly.
+When combining the wet and dry ingredients, it's essential to mix only until everything is just combined. Overmixing can develop the gluten in the flour, resulting in a denser and tougher cake rather than the tender crumb you desire. A gentle hand and a silicone spatula can help delicately incorporate the ingredients.
+### Folding in Chocolate Chips
+Folding is an important technique to keep the batter airy while adding your favorite chocolate chips. To fold effectively, start by scooping from the bottom of the bowl and bringing it up and over the top. Rotate the bowl after each fold to ensure even distribution without vigorously mixing. 
+When it comes to chocolate chips, consider using semi-sweet, dark, or even milk chocolate options based on your personal taste. Each type of chocolate will contribute a different flavor profile to your cake, allowing you to customize it to your liking.
+## Baking the Cake
+### Pouring the Batter
+When it's time to pour the batter into your prepared cake pan, aim for an even distribution. Pour the batter in the center and use an offset spatula to spread it gently towards the edges. This practice helps ensure the cake bakes uniformly. 
+To avoid large air pockets that can form as the cake bakes, tap the pan lightly on the counter before placing it in the oven. This action allows any trapped air bubbles to escape, promoting a smooth surface once baked.
+### Monitoring Baking Time
+Baking times can vary based on your oven, so keeping a close eye on your cake is essential. As it approaches the 25-minute mark, start checking for doneness. The toothpick test is a reliable method: insert a toothpick into the center of the cake, and it should come out clean or with a few moist crumbs clinging to it. This indicates your cake is perfectly baked.
+## Cooling the Cake
+### Why Cooling is Important
+Allowing the cake to cool sufficiently is vital to ensure the texture remains intact. When cake cools, steam escapes, preventing sogginess that can occur if you frost while still warm. Additionally, cooling helps the flavors meld and mature, enhancing the overall taste.
+To transfer your cake safely, run a spatula around the edges of the pan first. Then, carefully invert the cake onto a wire rack, giving it a gentle tap on the bottom to encourage it to release. 
+### Allowing it to Rest
+Letting your cake rest before icing is equally important, as this aids in achieving the ideal texture during serving. If you're in a hurry, you can place the cake in the refrigerator or freezer for a short time to speed up the cooling process. However, be cautious with this method; you don’t want the cake to freeze or become too firm.
+## Topping Your Dessert
+### Perfecting Whipped Cream
+Whipped cream can elevate your cake from delicious to extraordinary. While store-bought versions are convenient, making your own allows you to control the sweetness and texture. If you decide to whip cream at home, start with chilled heavy cream and whip until soft peaks form.
+Want to add a twist? Flavor your whipped cream with a dash of vanilla or almond extract, or even mix in a bit of cocoa powder for a chocolate twist. 
+### Final Touches
+Additional toppings can greatly enhance the presentation and flavor of your dessert. In addition to the whipped cream, consider drizzling chocolate syrup or sprinkling crushed nuts on top. For an eye-catching look, add edible flowers for a pop of color.
+For plating, consider using a cake stand or decorative plate to serve your cake. Just before serving, you may want to dust the entire dessert with powdered sugar for an elegant finish.
+## Serving Suggestions
+### Pairing Ideas
+Pairing your dessert with the right beverage can elevate the experience. A warm cup of coffee complements the rich chocolate perfectly, while milk can balance the sweetness if you prefer a more neutral option. If you're feeling adventurous, serve it alongside a sweet dessert wine, which can contrast beautifully with the chocolate flavor.
+In terms of flavors that complement chocolate, consider serving berries—strawberries, raspberries, or cherries. Their tartness adds a lovely contrast, while whipped cream can enhance the overall harmony of the dessert.
+### Presentation Techniques
+When it comes to slicing and serving, use a sharp knife to achieve clean, even slices. Wipe the knife with a damp cloth between cuts to maintain neat edges. For an eye-catching style, layer slices on each plate, alternating with fresh berries or additional whipped cream.
+Garnishing ideas include a sprig of mint, a chocolate curl, or a few extra chocolate chips on top. These small details can make your dessert not only delicious but also visually appealing.
+## Storing Leftovers
+### Best Practices for Storage
+To keep your cake fresh, store it in an airtight container. If the cake is frosted, it can remain at room temperature for a day or two, but beyond that, refrigeration is recommended. Place a piece of plastic wrap or parchment paper over the top before sealing to prevent dryness.
+For longer storage, consider freezing the cake. Wrap portions tightly in plastic wrap and then place them in a freezer bag. This method helps maintain flavor and moisture, allowing you to enjoy slices later on.
+### Reheating Instructions
+If you have leftover cake and want to enjoy it warm, reheating is simple. You can microwave individual slices for about 10-15 seconds, being careful not to overdo it, as the cake can dry out. For a larger piece, consider warming it in an oven set to 350°F (175°C) for about 5-10 minutes. 
+## Conclusion
+This viral dessert is not only easy to prepare but also boasts a rich chocolate flavor that's sure to delight. With its moist texture and the creaminess of whipped cream topping, it’s perfect for satisfying your sweet tooth in just 45 minutes. Whether for a family gathering or a quiet night in, this cake will surely become a favorite in your dessert repertoire.
+</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Easy Chocolate Cake Recipe for Desserts Everyone Will Love</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Easy Viral Chocolate Cake Recipe Everyone Is Raving About</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Decadent Chocolate Chip Cake Delight</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Indulge in the rich flavors of this easy viral chocolate cake recipe that everyone is raving about. Perfect for any occasion, this dessert is topped with fluffy whipped cream, making it a delightful treat for chocolate lovers. Whether you're an experienced baker or a novice in the kitchen, this simple recipe will bring joy to your celebrations and impress your guests.</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>dessert, chocolate cake, baking, viral recipe, whipped cream, easy recipe</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Viral Dessert Recipe</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Discover the viral dessert everyone is making right now! This easy chocolate cake recipe will satisfy your sweet cravings.</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Desktop/ho/ALL/A2-Pinterest_02-out/output_images/image_1.jpg</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-chocolate-cake-recipe-for-desserts-everyone-will-love-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Easy TikTok Dessert You Must Try</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Easy TikTok Dessert You Must Try 🍰✨
+Ingredients:
 - 1 cup heavy cream
-- 1 cup grated Parmesan cheese
-- Salt and pepper to taste
-- Fresh parsley, chopped (for garnish)
+- 1 cup condensed milk
+- 1 teaspoon vanilla extract
+- 1 cup crushed Oreos
+- 1/2 cup chocolate chips
 Instructions:
-1. Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.
-2. In a large skillet, heat the olive oil over medium heat. Add the sliced chicken breast and season with salt and pepper.
-3. Cook the chicken for about 5-7 minutes, or until it is golden brown and cooked through. Remove the chicken from the skillet and set aside.
-4. In the same skillet, add the minced garlic and sauté for about 1 minute until fragrant.
-5. Pour in the heavy cream and bring to a simmer. Stir in the Parmesan cheese until melted and the sauce is creamy.
-6. Add the cooked chicken back into the skillet and mix well to coat with the sauce.
-7. Toss the cooked fettuccine pasta into the skillet, combining everything evenly.
-8. Adjust seasoning with salt and pepper as needed.
-9. Serve hot, garnished with fresh parsley.
-Prep Time: 10 minutes
-Cook Time: 20 minutes
-Total Time: 30 minutes
-Course: Main Course
-Cuisine: Italian
-Servings: 4
-Calories: ~600 per serving</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-04-29 15:07:23</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+1. In a mixing bowl, combine heavy cream, condensed milk, and vanilla extract.
+2. Whip the mixture with an electric mixer until soft peaks form.
+3. Gently fold in the crushed Oreos and chocolate chips until evenly distributed.
+4. Transfer the mixture into a loaf pan, smoothing the top.
+5. Cover the pan with plastic wrap and freeze for at least 4 hours or until solid.
+6. Once frozen, remove from the freezer and let sit for 5 minutes to soften slightly.
+7. Slice into pieces and serve immediately, garnished with extra crushed Oreos if desired.
+Prep Time: 15 minutes
+Cook Time: 0 minutes
+Total Time: 4 hours 15 minutes
+Course: Dessert
+Cuisine: American
+Servings: 8
+Calories: ~250 per serving</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:59:17</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>{
-  "name": "Creamy Garlic Chicken Pasta",
-  "summary": "This creamy garlic chicken pasta is a delicious and comforting dish that combines tender chicken, fettuccine, and a rich garlic cream sauce. Perfect for a quick weeknight dinner.",
-  "servings": "4",
-  "prep_time": "10",
-  "cook_time": "20",
-  "total_time": "30",
-  "calories": "600",
-  "course": "Main Course",
-  "cuisine": "Italian",
+  "name": "Easy TikTok Dessert",
+  "summary": "This easy TikTok dessert combines whipped cream, condensed milk, and Oreos for a deliciously simple treat. Perfect for any occasion, it's sure to impress your friends and family.",
+  "servings": "8",
+  "prep_time": "15",
+  "cook_time": "0",
+  "total_time": "255",
+  "calories": "250",
+  "course": "Dessert",
+  "cuisine": "American",
   "keywords": [
-    "pasta",
-    "chicken",
-    "creamy",
-    "garlic",
-    "Italian",
-    "dinner"
+    "dessert",
+    "easy",
+    "TikTok",
+    "Oreo",
+    "no bake"
   ],
-  "notes": "Adjust seasoning to taste for a personalized flavor. Calories are per serving.",
+  "notes": "For best results, freeze overnight. Calories are per serving.",
   "ingredients": [
-    {
-      "amount": "8",
-      "unit": "oz",
-      "name": "fettuccine pasta"
-    },
-    {
-      "amount": "2",
-      "unit": "tablespoons",
-      "name": "olive oil"
-    },
-    {
-      "amount": "1",
-      "unit": "lb",
-      "name": "chicken breast, sliced into strips"
-    },
-    {
-      "amount": "4",
-      "unit": "cloves",
-      "name": "garlic, minced"
-    },
     {
       "amount": "1",
       "unit": "cup",
@@ -552,41 +1056,699 @@
     {
       "amount": "1",
       "unit": "cup",
-      "name": "grated Parmesan cheese"
-    },
-    {
-      "amount": "",
-      "unit": "",
-      "name": "Salt and pepper to taste"
-    },
-    {
-      "amount": "",
-      "unit": "",
-      "name": "Fresh parsley, chopped (for garnish)"
+      "name": "condensed milk"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "vanilla extract"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "crushed Oreos"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "chocolate chips"
     }
   ],
   "instructions": [
-    "Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.",
-    "In a large skillet, heat the olive oil over medium heat. Add the sliced chicken breast and season with salt and pepper.",
-    "Cook the chicken for about 5-7 minutes, or until it is golden brown and cooked through. Remove the chicken from the skillet and set aside.",
-    "In the same skillet, add the minced garlic and sauté for about 1 minute until fragrant.",
-    "Pour in the heavy cream and bring to a simmer. Stir in the Parmesan cheese until melted and the sauce is creamy.",
-    "Add the cooked chicken back into the skillet and mix well to coat with the sauce.",
-    "Toss the cooked fettuccine pasta into the skillet, combining everything evenly.",
-    "Adjust seasoning with salt and pepper as needed.",
-    "Serve hot, garnished with fresh parsley."
+    "In a mixing bowl, combine heavy cream, condensed milk, and vanilla extract.",
+    "Whip the mixture with an electric mixer until soft peaks form.",
+    "Gently fold in the crushed Oreos and chocolate chips until evenly distributed.",
+    "Transfer the mixture into a loaf pan, smoothing the top.",
+    "Cover the pan with plastic wrap and freeze for at least 240 minutes or until solid.",
+    "Once frozen, remove from the freezer and let sit for 5 minutes to soften slightly.",
+    "Slice into pieces and serve immediately, garnished with extra crushed Oreos if desired."
   ]
 }</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of creamy garlic chicken pasta served in a clean white ceramic bowl, showcasing the fettuccine coated in a rich sauce, tender chicken strips, and a sprinkle of fresh parsley on top, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>fettuccine pasta, olive oil, chicken breast, garlic, heavy cream, Parmesan cheese, salt, pepper, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of a frozen Oreo dessert sliced and plated in a clean white ceramic bowl, garnished with extra crushed Oreos, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the food center, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>heavy cream, condensed milk, vanilla extract, crushed Oreos, chocolate chips, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0521001/c856160865f.png</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/47ace4043e2.png</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/a14fbe43c63.png</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/f04afba2d52.png</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521001/38ae208399b.png</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0521001/83a802d1a54.png</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/1b8ba8a9283.png</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/05e4921ed01.png</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/3c969cd1fed.png</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521001/980d63d9a22.png</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy TikTok Dessert You Must Try
+## Introduction
+The world of desserts has undergone a delightful transformation, and one particular treat has taken social media by storm—this Easy TikTok Dessert. Combining a rich, creamy texture with the delightful crunch of Oreos and the sweet surprise of chocolate chips, this dessert has earned its place as a favorite among dessert lovers. Whether you're looking for a unique ending to a festive meal or simply want a sweet treat to enjoy while binge-watching your favorite show, this dish does not disappoint. Its simple, no-bake preparation ensures that it fits perfectly into both casual weekdays and special occasions alike.
+This dessert showcases how easy it can be to create something spectacular with minimal effort. The majority of your time is spent letting it freeze, allowing the flavors to meld beautifully while you sit back, relax, and anticipate the deliciousness to come. Friends and family will surely be dazzled by not only its layered look but also its balance of flavors and textures. This Easy TikTok Dessert isn't just a delightful choice; it's a showstopper that proves dessert mastery doesn't always require extraordinary skills or extensive kitchen gadgets.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 0 minutes
+- Total Time: 4 hours 15 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 8
+- Calories: ~250 per serving
+## Ingredients
+### The success of this dessert lies in its straightforward yet essential components:
+- 1 cup heavy cream
+- 1 cup condensed milk
+- 1 teaspoon vanilla extract
+- 1 cup crushed Oreos
+- 1/2 cup chocolate chips
+Using high-quality ingredients can significantly enhance the flavor of your dessert. Fresh heavy cream, standard store-bought condensed milk, and real vanilla extract carry enough richness to create a satisfying blend. Whenever possible, choose cream with a high fat percentage for a creamier texture. As for Oreos, feel free to experiment with both classic and flavored varieties to add a unique twist to your dessert. As you gather your ingredients, consider any potential substitutions that suit your taste preferences, but remember that the richness of this dessert predominantly relies on these key elements.
+{{image_ing_1}}
+## Instructions
+1. In a mixing bowl, combine heavy cream, condensed milk, and vanilla extract.
+2. Whip the mixture with an electric mixer until soft peaks form.
+3. Gently fold in the crushed Oreos and chocolate chips until evenly distributed.
+4. Transfer the mixture into a loaf pan, smoothing the top.
+5. Cover the pan with plastic wrap and freeze for at least 4 hours or until solid.
+6. Once frozen, remove from the freezer and let sit for 5 minutes to soften slightly.
+7. Slice into pieces and serve immediately, garnished with extra crushed Oreos if desired.
+## Preparation Steps
+Embarking on the journey to create this Easy TikTok Dessert begins with a few simple yet vital steps. To start, carefully combine the heavy cream, condensed milk, and vanilla extract in a mixing bowl. This mixture sets the foundation for a sweet, creamy delight that will pamper your taste buds.
+Using an electric mixer, whip the combined ingredients. This is where the magic begins—you'll want to achieve soft peaks, which are crucial for the dessert's texture. This process is vital in ensuring that your foundation is both fluffy and stable for the remaining additions. It's critical to pay attention during this phase, as the right consistency will contribute significantly to the overall success of your dessert.
+With a smooth base established, it's time to introduce the crushed Oreos and chocolate chips. Gently folding these into the whipped mixture is an essential step, as it helps maintain the airy texture you've worked hard to create. Careful folding means incorporating the crispy texture of the Oreos and the little bursts of sweetness from the chocolate chips without deflating your mixture.
+Once everything is combined, transfer your luscious creation into a loaf pan. Smoothing the top ensures a beautiful presentation once it's time to serve. After you've covered the pan with plastic wrap, off it goes into the freezer. This waiting period—at least 4 hours—is not just for chilling; it's for the flavors to meld and deepen.
+## The Whipping Process
+Achieving soft peaks is a pivotal moment in the creation of your dessert. So, what exactly does “soft peaks” mean? When you whip heavy cream, tiny bubbles form that create an airy structure—it is essential to achieve this lightness. Soft peaks are reached when the mixture is whipped just enough that when you lift your whisk or mixer, the cream holds a gentle curve yet can still smoothly melt back into itself. 
+Temperature plays a crucial role in this process: starting with well-chilled heavy cream will yield better results as colder cream whips up faster and easier. Avoid the temptations to over-whip; this can turn the light, fluffy cream into a grainy, butter-like texture, and you definitely don’t want that for this dessert! 
+Timing is everything when it comes to this step. Keep a keen eye on your mixer—stop whipping as soon as those soft peaks form, rather than letting your desire for a firmer texture lead you astray.
+## Crafting the Mixture
+The melding of the whipped cream, condensed milk, and vanilla is what will define the overall flavor and texture of your Easy TikTok Dessert. Each ingredient plays a specific role: the heavy cream brings creaminess and volume, the condensed milk adds sweetness and depth, while the vanilla extract lifts the entire flavor profile, creating a harmonious balance.
+Combining these ingredients should be done carefully and thoroughly. You want the whipped mixture to remain airy while ensuring that the condensed milk and vanilla are evenly distributed throughout. This ensures that every bite bursts with flavor without sacrificing the delightful texture that you achieved during the whipping process.
+As you mix, think about other potential flavorings or mix-ins you might want to explore. While Oreos and chocolate chips are a classic combination, consider adding in peanut butter for a nutty twist, or perhaps some fresh fruit like strawberries for a refreshing note. This dessert is wonderfully versatile, allowing you to customize it according to your mood or the occasion.
+## Incorporating Oreos and Chocolate Chips
+Once your base is ready, adding the crushed Oreos and chocolate chips requires an element of finesse. Crushing Oreos can be a delightful experience—place them in a resealable bag and give them a good roll with a rolling pin, or pulse them in a food processor for a finer crumb. Both methods work well, but be mindful of how large you want your chunks to be; larger pieces provide a satisfying crunch, while finer crumbs blend into the mixture more seamlessly.
+Distributing these additions evenly throughout the mixture is critical for consistent flavor across every slice. The texture of the Oreos contrasts beautifully with the creaminess of the base, while the chocolate chips lend an additional touch of sweetness and richness to the dessert. Aim to fold these components into your mixture gently; this will ensure that they are perfectly integrated without deflating those lovely soft peaks you’ve achieved.
+### Variations using different types of cookies or chocolates
+While the original recipe is delightful and rich, experimenting with different types of cookies or chocolates can add exciting new flavors to this Easy TikTok Dessert. Rather than just using Oreos, consider trying chocolate chip cookies for a classic twist, or gingersnaps for a pinch of spice. You can also mix in flavored creams like mint or peanut butter, which can complement the chocolate beautifully.
+For a fruitier version, consider crushed vanilla wafers or lemon-flavored cookies, allowing the sweet and tangy profile to shine through in each bite. You might also explore using flavored chocolate chips, such as white chocolate or butterscotch, which can add another layer of sweetness and complexity to the dessert. The key is to ensure that whatever cookie or chocolate you choose complements the creamy base of heavy cream and condensed milk.
+## Freezing and Setting
+### Importance of proper freezing techniques
+One crucial aspect of making the Easy TikTok Dessert is ensuring that the mixture is properly frozen. The freezing process is what transforms your sweet combination into the delightful treat that can be sliced and enjoyed. Improper freezing may lead to an unpleasant texture or could result in a dessert that doesn't set fully. Therefore, it is essential to use a loaf pan that allows for even freezing throughout.
+Explanation of how long to freeze and what to look for when it’s ready
+Once you’ve prepared the mixture and placed it into the loaf pan, the waiting period begins. The recipe recommends a freezing time of at least 4 hours. During this time, it’s crucial to ensure that the dessert is solid before serving. You’ll know it’s ready when the surface feels firm to the touch and shows no signs of being mushy or soft. A properly frozen dessert should hold its shape well when sliced.
+### Tips to avoid ice crystals for a smoother texture
+To achieve the smoothest texture and avoid pesky ice crystals, consider covering the loaf pan with plastic wrap or even a lid. This will protect the dessert from air exposure, which can lead to unwanted ice crystal formation. Additionally, freezing the dessert in a metal pan can provide optimal chilling because metal conducts cold better than glass or plastic. If you find that your dessert develops ice crystals, gently press them down before serving for a creamier consistency.
+## Serving Suggestions
+### Creative ways to present the dessert
+A dessert as visually appealing as this deserves an equally stunning presentation. To serve, consider placing the slices on a chilled plate, which can help maintain their texture for a longer duration. You might also want to layer servings with additional crushed Oreos sprinkled on top for a striking contrast against the white dessert. For an extra upscale touch, serve in clear dessert cups, showcasing the layers of crushed cookies and cream.
+### Garnishing ideas with extra Oreos or chocolate shavings
+Garnishing is essential for adding that finishing touch. Simple toppings like additional crushed Oreos add a crunchy texture while enhancing the flavor. A sprinkle of chocolate shavings, fresh whipped cream, or even a drizzle of chocolate sauce can elevate the dessert’s richness. Other great options include crushed nuts for a bit of saltiness and texture, or a dusting of cocoa powder for an added visual impact.
+### Pairing the dessert with beverages for enhanced enjoyment
+Complementing this dessert with a drink can enhance the overall experience. Consider pairing it with a glass of cold milk, which offers a classic combination with cookies and cream flavors. For adults, a rich coffee or an espresso can balance the sweetness beautifully. Alternatively, a milkshake made with vanilla ice cream or a light sparkling beverage can keep the dessert feeling fresh and elevate the indulgence.
+## Nutritional Information
+### Breakdown of calories per serving
+When it comes to indulgent desserts, knowing the calorie count helps in managing portion sizes. Each serving of this Easy TikTok Dessert is approximately 250 calories, making it a sweet treat that doesn’t overdo it. The base of the dessert, featuring heavy cream and condensed milk, combines to create a luscious texture, while the Oreos and chocolate chips add bursts of flavor but also contribute to the overall caloric content.
+### Overview of key nutritional factors
+Aside from calories, this dessert has notable nutritional factors worth mentioning. The heavy cream offers a source of fats, providing a rich mouthfeel, and the sweetened condensed milk contributes a significant amount of sugars. If you are mindful of sugar intake, this information can help you decide how many servings you wish to enjoy. 
+### Discussion of the dessert's suitability for various dietary preferences
+The Easy TikTok Dessert, while splendidly indulgent, is primarily milk-based and includes gluten from the Oreos. Therefore, it may not be suitable for those with gluten intolerance or lactose sensitivity. Variations using gluten-free cookies can help make this treat more accessible, and dairy-free alternatives for the cream and condensed milk are available, which could cater to vegan diets with some careful ingredient substitutions.
+## Common Mistakes to Avoid
+### Over-whipping the cream
+One common mistake when preparing this dessert is over-whipping the heavy cream. While the goal is to create soft peaks, whipping too much can lead to butter-like texture rather than maintaining a smooth blend with the other ingredients. Monitoring the consistency closely while whipping is key.
+### Misjudging the freezing time
+Misjudging the freezing time can result in a dessert that is either too soft or overly firm. Always stick to the suggested freezing time and check for the correct firmness before serving. If the dessert hasn’t set enough, it won't slice properly, and if it freezes too long, it may become overly hard.
+### Skipping the letting sit time before serving
+Skipping the recommended waiting period before slicing can make for a challenging serving experience. Letting the dessert sit for about 5 minutes after removing it from the freezer allows the outer sections to soften just enough to create perfect slices, without compromising the integrity of the dessert.
+## Storage Tips
+### Best practices for storing leftovers
+If you find yourself with leftovers, proper storage is essential to maintaining the quality of this dessert. Cover the loaf pan tightly with plastic wrap or transfer the slices into an airtight container. This will help prevent freezer burn and preserve the delicious taste.
+### Duration for which the dessert remains fresh in the freezer
+When stored correctly, the Easy TikTok Dessert can remain fresh in the freezer for up to 2 weeks. However, for optimal taste and texture, it is best enjoyed within the first week.
+### Potential for repurposing in other recipes or snacks
+If you have leftover slices that you’re not ready to eat, consider repurposing the dessert. Crumbled pieces can be added to milkshakes, blended into ice cream, or layered in parfaits. This versatility can help minimize waste while still delivering a delicious treat.
+## Conclusion
+This Easy TikTok Dessert is a delectable treat with a creamy texture and rich flavors from heavy cream, Oreos, and chocolate chips. With a quick preparation time and a waiting period mostly spent in the freezer, this dish offers a marvelous blend of ease and taste, perfect for any occasion. By exploring variations, proper freezing techniques, and creative serving options, this dessert is sure to be a crowd-pleaser at gatherings or a satisfying treat for yourself.
+</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Easy TikTok Dessert You Must Try</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>No-Bake Oreo Chocolate Dessert Recipe from TikTok</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Oreo Ice Cream Delight</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Indulge in the ultimate easy dessert with this No-Bake Oreo Chocolate Dessert recipe inspired by TikTok. Perfect for hot summer days, this delightful frozen treat combines creamy layers of Oreos and chocolate chips, making it a crowd-pleaser for any occasion. Treat yourself to a quick and delicious dessert that requires no baking and is sure to impress family and friends.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>easy dessert, TikTok recipe, Oreos, no-bake, chocolate chips, frozen treat</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Easy TikTok Dessert</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Try this easy TikTok dessert recipe! Delight in a creamy Oreo treat that's perfect for any sweet craving. 🍰✨</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Desktop/ho/ALL/A2-Pinterest_02-out/output_images/image_2.jpg</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-tiktok-dessert-you-must-try-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dessert Everyone Is Obsessed With</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dessert Everyone Is Obsessed With 🍰😍
+Ingredients:
+- 1 cup all-purpose flour
+- 1/2 cup unsweetened cocoa powder
+- 1 cup granulated sugar
+- 1/2 cup unsalted butter, softened
+- 2 large eggs
+- 1 teaspoon vanilla extract
+- 1/2 teaspoon baking powder
+- 1/4 teaspoon salt
+- 1 cup chocolate chips
+- 1/2 cup heavy cream
+Instructions:
+1. Preheat your oven to 350°F (175°C) and grease an 8-inch square baking pan.
+2. In a mixing bowl, cream together the softened butter and sugar until light and fluffy.
+3. Add the eggs one at a time, mixing well after each addition, then stir in the vanilla extract.
+4. In another bowl, sift together the flour, cocoa powder, baking powder, and salt.
+5. Gradually add the dry ingredients to the wet mixture, stirring until just combined.
+6. Fold in the chocolate chips until evenly distributed throughout the batter.
+7. Pour the batter into the prepared baking pan and smooth the top with a spatula.
+8. Bake for 25-30 minutes, or until a toothpick inserted into the center comes out with a few moist crumbs.
+9. While the brownies are baking, heat the heavy cream in a small saucepan until just simmering, then pour it over any remaining chocolate chips in a bowl to create a ganache.
+10. Once the brownies are done, let them cool in the pan for 10 minutes before transferring them to a wire rack.
+11. Drizzle the chocolate ganache over the cooled brownies before slicing into squares.
+Prep Time: 15 minutes
+Cook Time: 30 minutes
+Total Time: 45 minutes
+Course: Dessert
+Cuisine: American
+Servings: 16
+Calories: ~250 per serving</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-21 00:59:33</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{
+  "name": "Dessert Everyone Is Obsessed With",
+  "summary": "This decadent dessert combines rich chocolate flavors with a creamy ganache, making it a favorite among chocolate lovers. Perfect for any occasion, these brownies are sure to impress.",
+  "servings": "16",
+  "prep_time": "15",
+  "cook_time": "30",
+  "total_time": "45",
+  "calories": "250",
+  "course": "Dessert",
+  "cuisine": "American",
+  "keywords": [
+    "brownies",
+    "chocolate",
+    "dessert",
+    "ganache",
+    "easy recipe"
+  ],
+  "notes": "For a richer flavor, use high-quality chocolate chips. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "all-purpose flour"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "unsweetened cocoa powder"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "granulated sugar"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "unsalted butter, softened"
+    },
+    {
+      "amount": "2",
+      "unit": "large",
+      "name": "eggs"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "vanilla extract"
+    },
+    {
+      "amount": "½",
+      "unit": "teaspoon",
+      "name": "baking powder"
+    },
+    {
+      "amount": "¼",
+      "unit": "teaspoon",
+      "name": "salt"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "chocolate chips"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "heavy cream"
+    }
+  ],
+  "instructions": [
+    "Preheat your oven to 350°F (175°C) and grease an 8-inch square baking pan.",
+    "In a mixing bowl, cream together the softened butter and sugar until light and fluffy.",
+    "Add the eggs one at a time, mixing well after each addition, then stir in the vanilla extract.",
+    "In another bowl, sift together the flour, cocoa powder, baking powder, and salt.",
+    "Gradually add the dry ingredients to the wet mixture, stirring until just combined.",
+    "Fold in the chocolate chips until evenly distributed throughout the batter.",
+    "Pour the batter into the prepared baking pan and smooth the top with a spatula.",
+    "Bake for 25-30 minutes, or until a toothpick inserted into the center comes out with a few moist crumbs.",
+    "While the brownies are baking, heat the heavy cream in a small saucepan until just simmering, then pour it over any remaining chocolate chips in a bowl to create a ganache.",
+    "Once the brownies are done, let them cool in the pan for 10 minutes before transferring them to a wire rack.",
+    "Drizzle the chocolate ganache over the cooled brownies before slicing into squares."
+  ]
+}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Realistic, appetizing ULTRA close-up of decadent chocolate brownies drizzled with glossy chocolate ganache, served in a clean white ceramic plate, on a light neutral surface. The composition fills 90–100% of the frame, showcasing the rich texture of the brownies and the smoothness of the ganache, with a shallow depth of field and soft natural daylight creating gentle shadows. Sharp focus at the center of the brownies, captured at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>flour, cocoa powder, sugar, butter, eggs, vanilla extract, baking powder, salt, chocolate chips, heavy cream, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0521002/7d5e27d3122.png</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521002/26a5e39e618.png</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521002/88fda423822.png</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521002/9192629eda3.png</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0521002/0a549730be5.png</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0521002/10e6b625f9b.png</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521002/d166823132c.png</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521002/f634ee881df.png</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521002/737a1346db1.png</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0521002/0c9ba0a4125.png</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy American Brownies with Chocolate Ganache Topping
+## Introduction
+Indulging in a rich, chocolatey dessert is one of life’s greatest pleasures, and this American brownie recipe is sure to become a favorite. With its perfect balance of fudgy texture and sweet chocolate flavor, it's an irresistible treat for any occasion. Brownies are the quintessential dessert, fitting for everything from casual family dinners to festive celebrations. Their warm, chocolatey appeal is universally loved, making them a go-to option for gatherings or simply enjoying a sweet moment at home.
+Crafting these brownies is delightfully straightforward, requiring minimal time and effort while delivering maximum satisfaction. Furthermore, the addition of luscious chocolate ganache elevates these treats to another level, adding an extra layer of decadence. In this article, we will delve into the details of crafting these brownies, complete with tips and tricks for making them even more delightful.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 30 minutes
+- Total Time: 45 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 16
+- Calories: ~250 per serving
+This classic brownie recipe is not only simple to make but is also sure to impress friends and family alike. Delve into the decadent flavors of chocolate, perfectly complemented by a luscious ganache topping. With a preparation time of just 15 minutes and a total baking time of 30 minutes, you can whip up a batch of these brownies in under an hour. These brownies serve 16 and come in at approximately 250 calories per serving.
+## Ingredients
+- 1 cup all-purpose flour
+- 1/2 cup unsweetened cocoa powder
+- 1 cup granulated sugar
+- 1/2 cup unsalted butter, softened
+- 2 large eggs
+- 1 teaspoon vanilla extract
+- 1/2 teaspoon baking powder
+- 1/4 teaspoon salt
+- 1 cup chocolate chips
+- 1/2 cup heavy cream
+In this recipe, each ingredient plays a pivotal role in creating the perfect brownie. The all-purpose flour provides the necessary structure; unsweetened cocoa powder gives it that rich chocolate flavor, while granulated sugar sweetens the treat. Softened unsalted butter adds moisture and richness, and eggs play a critical role in binding the ingredients together. Vanilla extract enhances the flavors, while baking powder serves as a leavening agent to ensure a delightful texture. A pinch of salt balances the sweetness beautifully. Finally, chocolate chips not only intensify the chocolate experience but also add delightful pockets of melty goodness. The heavy cream is essential for creating the simple yet divine chocolate ganache that finishes these brownies perfectly.
+{{image_ing_1}}
+## Instructions
+1. Preheat your oven to 350°F (175°C) and grease an 8-inch square baking pan.
+2. In a mixing bowl, cream together the softened butter and sugar until light and fluffy.
+3. Add the eggs one at a time, mixing well after each addition, then stir in the vanilla extract.
+4. In another bowl, sift together the flour, cocoa powder, baking powder, and salt.
+5. Gradually add the dry ingredients to the wet mixture, stirring until just combined.
+6. Fold in the chocolate chips until evenly distributed throughout the batter.
+7. Pour the batter into the prepared baking pan and smooth the top with a spatula.
+8. Bake for 25-30 minutes, or until a toothpick inserted into the center comes out with a few moist crumbs.
+9. While the brownies are baking, heat the heavy cream in a small saucepan until just simmering, then pour it over any remaining chocolate chips in a bowl to create a ganache.
+10. Once the brownies are done, let them cool in the pan for 10 minutes before transferring them to a wire rack.
+11. Drizzle the chocolate ganache over the cooled brownies before slicing into squares.
+## Preparation Steps
+When preparing these decadent brownies, following each step with precision ensures the best outcome. Let's break down the preparation steps for clarity.
+### Preheating the Oven
+Begin by preheating your oven to 350°F (175°C). This is the ideal temperature for baking brownies, ensuring they cook evenly and develop that perfect fudgy interior. Preheating is crucial as it allows the brownies to rise properly and sets the initial structure.
+### Creaming Butter and Sugar
+The next step involves creaming together the softened butter and granulated sugar. Ensure that the butter is at room temperature so that it blends seamlessly with the sugar, creating a light, fluffy texture. This process incorporates air into the mixture, which is vital for achieving that delightful, tender crumb characteristic of great brownies. Aim for a pale, creamy consistency before proceeding.
+### Incorporating Eggs
+Add the eggs to the creamed butter-sugar mixture one at a time. This sequential incorporation is essential; it allows each egg to emulsify into the batter effectively. Mix until the egg is fully integrated before adding the next one. The liquid from the eggs helps with moisture and structure, making them a necessary component in this recipe.
+### Combining Dry Ingredients
+In a separate bowl, sift together the all-purpose flour, unsweetened cocoa powder, baking powder, and salt. Sifting not only eliminates lumps but also aerates the dry ingredients, which aids in their integration into the wet mixture. This step ensures that the brownies have a uniform texture and prevents clumping of the cocoa powder.
+### Folding in Chocolate Chips
+Finally, the last crucial step is to fold in the chocolate chips. Gently incorporate them into the batter using a spatula or wooden spoon, being careful not to overmix. The folding technique ensures that the chocolate chips are evenly distributed without deflating the batter's air bubbles. This step guarantees that every bite of brownie is bursting with sweet, chocolatey goodness.
+As you follow these preparation steps, you’ll be well on your way to creating the perfect batch of brownies that everyone will rave about. Each stage of the process contributes to the overall texture and flavor, resulting in a dessert that’s nostalgic yet impressively decadent.
+## Baking the Brownies
+When it comes to baking brownies, achieving the perfect texture is an essential part of the process. Whether you prefer chewy, fudgy, or cakey brownies, there are specific tips and techniques that can help you obtain your desired result.
+### Tips for Achieving the Perfect Brownie Texture
+To ensure your brownies come out perfectly every time, consider the following tips:
+- Utilize fresh ingredients: Using ingredients that are close to their expiration date can negatively impact the outcome. Always use fresh eggs, butter, and leavening agents.
+- Measure accurately: Brownies rely heavily on accurate measurements. Use a kitchen scale if you have one to ensure precision in your ingredients.
+- Don't overmix the batter: Once you incorporate the dry ingredients into the wet ingredients, mix just until combined. Overmixing can lead to tough brownies.
+- Pay attention to the baking time: Each oven is unique, so the recommended baking time may vary. Keeping a close eye on the brownies is essential.
+### Importance of Checking Doneness
+Knowing when your brownies are done is crucial to achieving a moist and fudgy result. The top should be set and have a slight gloss, while a toothpick inserted into the center should come out with a few moist crumbs but not wet batter.
+### Adjusting Bake Time
+Various factors can affect baking times, including the type of pan you use, your oven's calibration, and the specific ingredients. Dark pans tend to absorb heat more quickly, which could result in a shorter baking time compared to light-colored pans.
+### How to Test Brownies for Doneness
+The tried-and-true method for checking if your brownies are done is the toothpick test. Insert a toothpick into the center of the brownies, and if it comes out with a few moist crumbs stuck to it, they are perfectly baked. If the toothpick comes out with wet batter, they need a few additional minutes in the oven.
+### Cooling Process
+The cooling process plays a critical role in the texture of your brownies. If you cut them too soon, they might fall apart and lose their desirable fudgy consistency.
+### Why Cooling is Necessary Before Cutting
+Allowing the brownies to cool for at least 10 minutes in the pan helps them firm up. This cooling time lets the structure stabilize, making them easier to cut.
+### Techniques for Transferring Brownies Safely
+To transfer the brownies from the baking pan to a wire rack, use a spatula or carefully nudge them out with your hands, if possible. If you have lined the baking pan with parchment paper, you can lift the brownies out using the edges of the parchment, providing an easy way to remove them without mess.
+## Making the Ganache
+The chocolate ganache is the finishing touch that will elevate your brownies to a whole new level of decadence. The creamy richness complements the fudgy texture, creating a dessert that's hard to resist.
+### Step-by-Step Guide to Preparing Chocolate Ganache
+1. Start by heating the heavy cream in a small saucepan over medium-low heat until it just starts to simmer.
+2. Place your remaining chocolate chips in a heatproof bowl.
+3. Pour the hot cream over the chocolate chips, allowing them to sit for a couple of minutes.
+4. After a couple of minutes, gently stir the mixture using a whisk or spatula until smooth and shiny.
+### Alternative Methods for Melting Chocolate
+If you don't have a stovetop, you can alternatively melt chocolate by using a microwave. Place chocolate chips in a microwave-safe bowl and heat in 30-second intervals, stirring between each, until melted and smooth.
+### Heating the Cream
+Care needs to be taken when heating the cream. If you accidentally boil it, the texture and flavor of your ganache can suffer.
+### Importance of Not Overheating
+Check for tiny bubbles around the edges of the cream, which indicates it's ready. If you allow the cream to boil, it may curdle or cause the ganache to separate.
+### Signs that Cream Is at the Right Temperature
+You want the heavy cream to be just simmering, showing signs of small bubbles around the edges. This temperature activates the chocolate, making it easier to blend.
+### Combining with Chocolate Chips
+Achieving a smooth consistency in ganache is key and relies heavily on how well the chocolate integrates with the heated cream.
+### How to Store Leftover Ganache
+If you have any leftover ganache, allow it to cool completely before transferring it to an airtight container. You can store it in the refrigerator for up to a week or even freeze it for longer storage options.
+## Serving Suggestions
+Presenting your brownies can be just as delightful as making them. There are numerous fun ways to enhance the visuals and taste.
+### Fun Ways to Present Brownies Creatively
+Consider cutting the brownies into shapes or drizzling ganache artistically. A sprinkling of powdered sugar or cocoa can add an eye-catching touch.
+### Pairing Ideas with Ice Cream, Whipped Cream, or Fruit
+Serving brownies with a scoop of vanilla ice cream, a dollop of whipped cream, or fresh fruits like raspberries and strawberries can take your dessert experience to the next level.
+### Garnishing Options
+Enhancing your brownies with simple garnishes can truly elevate their appearance and flavor.
+- **Nuts:** Consider adding chopped walnuts or pecans on top to create an added crunch.
+- **Sprinkles:** Colorful sprinkles can bring a festive feel to your dessert.
+- **Sea Salt:** A light sprinkle of flaked sea salt can balance the sweetness and enhance the chocolate flavor.
+### Ways to Enhance Presentation
+Creating an aesthetic presentation can convert a simple dessert into a showstopper. Consider using square or rectangular cuts and serving them on pretty platters or in individual portions.
+## Storing Leftover Brownies
+Understanding the proper way to store brownies can keep them fresh and delicious for longer periods.
+### Best Practices for Maintaining Freshness
+To keep brownies fresh, store them in an airtight container at room temperature for several days. Avoid covering them with plastic wrap directly as it may create moisture.
+### Techniques for Freezing Brownies for Longer Storage
+If you're not planning to eat the brownies within a week, freezing is a great option. Wrap each brownie individually in plastic wrap, then place them in a freezer-safe container to minimize moisture exposure.
+### Refrigerating Brownies
+Refrigeration can sometimes alter the texture of brownies; however, if you choose to do so, allow them to cool completely before storing in a sealed container.
+### Tips for Proper Storage in the Refrigerator
+Ensure that brownies are wrapped tightly to prevent them from absorbing odors from other foods in the refrigerator, which can adversely affect their taste.
+### How Refrigeration Affects Texture
+Refrigeration can cause brownies to become denser and slightly firmer, so if you're a fan of that chewy texture, consuming them at room temperature after chilling is recommended.
+### Freezing Instructions
+If you’re looking to preserve your brownies for a longer time, here’s how to freeze them properly.
+- Allow brownies to cool entirely before slicing.
+- Wrap each portion tightly in plastic wrap.
+- Store wrapped brownies in a freezer-safe bag or container.
+- Label with the date and use within three months for optimal taste.
+### Thawing Guidelines for Optimal Taste
+To enjoy your brownies after freezing, transfer them to the refrigerator to thaw overnight or let them sit at room temperature for a couple of hours before indulging.
+## Common Brownie Mistakes to Avoid
+Being aware of common mistakes can help prevent frustrating baking experiences.
+### Common Pitfalls During Preparation and Baking
+Adjusting to baking times and oven temperatures is key. Each oven is unique and may require adjustments.
+### Tips for Troubleshooting Issues with Texture and Flavor
+If your brownies turn out dry, it may stem from overbaking or too much flour. On the flip side, if they are too gooey, try baking them slightly longer or lowering the oven temperature.
+### Underbaking and Overbaking
+Identify signs of underbaking by looking for a wet, batter-like consistency in the middle. Conversely, overbaked brownies will be dry and crumbly.
+### Texture Problems
+Texture issues can often arise from using outdated ingredients or measuring inaccuracies. Experimenting with ingredient ratios can help hone in on your ideal consistency.
+### What Can Cause Dry or Overly Dense Brownies
+Most texture problems stem from incorrect measurements, overmixing, or baking them too long. It may take some trial and error to get them just right, so don’t hesitate to note adjustments for future baking sessions.
+## Healthier Variations
+For those looking for healthier options, consider making substitutions that maintain taste while cutting down on calories and sugar.
+### Opportunities for Healthier Swaps
+Swapping out refined sugar for natural sweeteners like agave syrup or maple syrup can add a healthier touch without compromising flavor.
+### Tips for Reducing Sugar Without Compromising Flavor
+Use pureed fruits like applesauce or mashed bananas to retain moisture and sweetness while reducing the calorie count.
+### Gluten-Free Adaptations
+For individuals with gluten sensitivity, substituting regular flour with gluten-free flour blends will allow everyone to enjoy these delicious brownies.
+### Substitutes for Flour
+Coconut flour or almond flour can act as great substitutes, but adjust the ratios to accommodate their different absorption properties. 
+### Tips for Maintaining Texture in Gluten-Free Brownies
+Incorporating additional moisture, such as yogurt or eggs, can help prevent gluten-free brownie recipes from becoming overly dry or crumbly.
+## Conclusion
+These brownies are a delightful blend of rich flavors and fudgy textures. With careful attention to detail in their preparation and baking, you're sure to create a treat that stands out for any occasion. Enjoy the process and savor the rewards of your delicious endeavor.
+</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Easy American Brownies with Chocolate Ganache Topping</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Decadent Brownies with Chocolate Ganache Everyone Will Love</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Decadent Chocolate Chip Brownies</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Indulge in these decadent brownies topped with rich chocolate ganache, making them the ultimate dessert for any occasion. This easy recipe transforms simple ingredients into a luscious treat that everyone will love, perfect for gatherings or cozy nights in. Experience the joy of baking as these delightful brownies become a new favorite in your home.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>brownies, dessert, chocolate, baking, ganache, easy recipe</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Chocolate Brownie Dessert</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Indulge in the dessert everyone is obsessed with! Easy, decadent brownies topped with rich chocolate ganache. 🍰✨</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>dessert</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Desktop/ho/ALL/A2-Pinterest_02-out/output_images/image_3.jpg</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-american-brownies-with-chocolate-ganache-topping-2/</t>
         </is>
       </c>
     </row>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-chocolate-cake-recipe-for-desserts-everyone-will-love-2/</t>
+          <t>https://lowcarbdaily.com/easy-chocolate-cake-recipe-for-desserts-everyone-will-love-5/</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-tiktok-dessert-you-must-try-2/</t>
+          <t>https://lowcarbdaily.com/easy-tiktok-dessert-you-must-try-5/</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-american-brownies-with-chocolate-ganache-topping-2/</t>
+          <t>https://lowcarbdaily.com/easy-american-brownies-with-chocolate-ganache-topping-5/</t>
         </is>
       </c>
     </row>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -986,7 +986,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-chocolate-cake-recipe-for-desserts-everyone-will-love-5/</t>
+          <t>https://lowcarbdaily.com/easy-chocolate-cake-recipe-for-desserts-everyone-will-love-6/</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-tiktok-dessert-you-must-try-5/</t>
+          <t>https://lowcarbdaily.com/easy-tiktok-dessert-you-must-try-6/</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>https://lowcarbdaily.com/easy-american-brownies-with-chocolate-ganache-topping-5/</t>
+          <t>https://lowcarbdaily.com/easy-american-brownies-with-chocolate-ganache-topping-6/</t>
         </is>
       </c>
     </row>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -679,7 +679,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523170/9b31c98a8d0.png</t>
@@ -710,7 +709,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -857,7 +855,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523170/49fae17ec8f.png</t>
@@ -888,7 +885,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1031,7 +1027,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/62613ce40b0.png</t>
@@ -1062,7 +1057,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1234,7 +1228,6 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/fc5bd93be4b.png</t>
@@ -1265,405 +1258,14 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dessert Everyone Is Obsessed With</t>
+          <t>Trending Dessert You Can Make at Home</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
-        <is>
-          <t>Dessert Everyone Is Obsessed With 🍰😍
-Ingredients:
-- 2 cups all-purpose flour
-- 1 cup granulated sugar
-- 1/2 cup unsweetened cocoa powder
-- 1 teaspoon baking soda
-- 1/2 teaspoon salt
-- 1 cup buttermilk
-- 1/2 cup vegetable oil
-- 2 large eggs
-- 2 teaspoons vanilla extract
-- 1 cup boiling water
-- 1 cup chocolate chips
-- Whipped cream for serving
-Instructions:
-1. Preheat your oven to 350°F (175°C) and grease a 9x13 inch baking pan.
-2. In a large bowl, sift together the flour, sugar, cocoa powder, baking soda, and salt.
-3. In another bowl, whisk together the buttermilk, vegetable oil, eggs, and vanilla extract until well combined.
-4. Gradually add the wet ingredients to the dry ingredients, mixing until just combined.
-5. Carefully stir in the boiling water until the batter is smooth and well incorporated.
-6. Fold in the chocolate chips until evenly distributed.
-7. Pour the batter into the prepared baking pan and smooth the top.
-8. Bake for 30-35 minutes, or until a toothpick inserted in the center comes out clean.
-9. Allow the cake to cool in the pan for 10 minutes, then transfer to a wire rack to cool completely.
-10. Serve slices topped with whipped cream for an extra touch of indulgence.
-Prep Time: 15 minutes
-Cook Time: 35 minutes
-Total Time: 50 minutes
-Course: Dessert
-Cuisine: American
-Servings: 12
-Calories: ~320 per serving</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-23 16:47:13</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>{
-  "name": "Dessert Everyone Is Obsessed With",
-  "summary": "This decadent chocolate cake is a crowd-pleaser, featuring rich flavors and a moist texture. Perfect for any occasion, it's topped with whipped cream for an indulgent finish.",
-  "servings": "12",
-  "prep_time": "15",
-  "cook_time": "35",
-  "total_time": "50",
-  "calories": "320",
-  "course": "Dessert",
-  "cuisine": "American",
-  "keywords": [
-    "chocolate cake",
-    "dessert",
-    "easy recipe",
-    "baking",
-    "whipped cream"
-  ],
-  "notes": "For best results, use high-quality cocoa powder. Calories are per serving.",
-  "ingredients": [
-    {
-      "amount": "2",
-      "unit": "cups",
-      "name": "all-purpose flour"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "granulated sugar"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "unsweetened cocoa powder"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "baking soda"
-    },
-    {
-      "amount": "½",
-      "unit": "teaspoon",
-      "name": "salt"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "buttermilk"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "vegetable oil"
-    },
-    {
-      "amount": "2",
-      "unit": "large",
-      "name": "eggs"
-    },
-    {
-      "amount": "2",
-      "unit": "teaspoons",
-      "name": "vanilla extract"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "boiling water"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "chocolate chips"
-    },
-    {
-      "amount": "",
-      "unit": "",
-      "name": "Whipped cream for serving"
-    }
-  ],
-  "instructions": [
-    "Preheat your oven to 350°F (175°C) and grease a 9x13 inch baking pan.",
-    "In a large bowl, sift together the flour, sugar, cocoa powder, baking soda, and salt.",
-    "In another bowl, whisk together the buttermilk, vegetable oil, eggs, and vanilla extract until well combined.",
-    "Gradually add the wet ingredients to the dry ingredients, mixing until just combined.",
-    "Carefully stir in the boiling water until the batter is smooth and well incorporated.",
-    "Fold in the chocolate chips until evenly distributed.",
-    "Pour the batter into the prepared baking pan and smooth the top.",
-    "Bake for 30-35 minutes, or until a toothpick inserted in the center comes out clean.",
-    "Allow the cake to cool in the pan for 10 minutes, then transfer to a wire rack to cool completely.",
-    "Serve slices topped with whipped cream for an extra touch of indulgence."
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of a decadent chocolate cake slice topped with fluffy whipped cream, served in a clean white ceramic plate. The rich texture of the chocolate cake is visible, with melting chocolate chips glistening on top and a light sprinkle of cocoa powder. Soft natural daylight casts gentle shadows, enhancing the cake's details. The composition fills the frame, with a shallow depth of field drawing focus to the cake center, captured at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>flour, sugar, cocoa powder, baking soda, salt, buttermilk, vegetable oil, eggs, vanilla extract, boiling water, chocolate chips, whipped cream, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>task status failed: {'request': {'channel': '1441888792192618647', 'stream': False, 'prompt': "Realistic, appetizing ULTRA close-up of a decadent chocolate cake slice topped with fluffy whipped cream, served in a clean w</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/c61a9e43f4a.png</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/8dfd5a6a9a5.png</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/c4b4bd58d76.png</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/bb72146275f.png</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/ac389b05b6b.png</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Easy Dessert That Broke the Internet</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Easy Dessert That Broke the Internet 🍰🌍
-Ingredients:
-- 1 cup all-purpose flour
-- 1/2 cup granulated sugar
-- 1/2 cup unsweetened cocoa powder
-- 1 teaspoon baking powder
-- 1/4 teaspoon salt
-- 1/2 cup unsalted butter, melted
-- 2 large eggs
-- 1 teaspoon vanilla extract
-- 1 cup chocolate chips
-- 1/2 cup colorful sprinkles
-Instructions:
-1. Preheat your oven to 350°F (175°C) and grease an 8x8 inch baking dish.
-2. In a large mixing bowl, whisk together the flour, sugar, cocoa powder, baking powder, and salt until well combined.
-3. In a separate bowl, mix the melted butter, eggs, and vanilla extract until smooth.
-4. Pour the wet ingredients into the dry ingredients and stir until just combined.
-5. Fold in the chocolate chips and half of the colorful sprinkles.
-6. Pour the batter into the prepared baking dish and smooth the top with a spatula.
-7. Sprinkle the remaining colorful sprinkles on top of the batter.
-8. Bake for 25-30 minutes or until a toothpick inserted in the center comes out with a few moist crumbs.
-9. Allow to cool in the baking dish for 10 minutes, then transfer to a wire rack to cool completely.
-10. Cut into squares and serve with a scoop of ice cream for an extra treat!
-Prep Time: 10 minutes
-Cook Time: 30 minutes
-Total Time: 40 minutes
-Course: Dessert
-Cuisine: American
-Servings: 9
-Calories: ~250 per serving</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-23 16:47:19</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{
-  "name": "Easy Dessert That Broke the Internet",
-  "summary": "This delightful dessert combines chocolate and colorful sprinkles for a fun treat. It's easy to make and perfect for any occasion.",
-  "servings": "9",
-  "prep_time": "10",
-  "cook_time": "30",
-  "total_time": "40",
-  "calories": "250",
-  "course": "Dessert",
-  "cuisine": "American",
-  "keywords": [
-    "dessert",
-    "chocolate",
-    "easy",
-    "sprinkles",
-    "baking"
-  ],
-  "notes": "Serve with ice cream for an extra treat. Calories are per serving.",
-  "ingredients": [
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "all-purpose flour"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "granulated sugar"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "unsweetened cocoa powder"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "baking powder"
-    },
-    {
-      "amount": "¼",
-      "unit": "teaspoon",
-      "name": "salt"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "unsalted butter, melted"
-    },
-    {
-      "amount": "2",
-      "unit": "large",
-      "name": "eggs"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "vanilla extract"
-    },
-    {
-      "amount": "1",
-      "unit": "cup",
-      "name": "chocolate chips"
-    },
-    {
-      "amount": "½",
-      "unit": "cup",
-      "name": "colorful sprinkles"
-    }
-  ],
-  "instructions": [
-    "Preheat your oven to 350°F (175°C) and grease an 8x8 inch baking dish.",
-    "In a large mixing bowl, whisk together the flour, sugar, cocoa powder, baking powder, and salt until well combined.",
-    "In a separate bowl, mix the melted butter, eggs, and vanilla extract until smooth.",
-    "Pour the wet ingredients into the dry ingredients and stir until just combined.",
-    "Fold in the chocolate chips and half of the colorful sprinkles.",
-    "Pour the batter into the prepared baking dish and smooth the top with a spatula.",
-    "Sprinkle the remaining colorful sprinkles on top of the batter.",
-    "Bake for 25-30 minutes or until a toothpick inserted in the center comes out with a few moist crumbs.",
-    "Allow to cool in the baking dish for 10 minutes, then transfer to a wire rack to cool completely.",
-    "Cut into squares and serve with a scoop of ice cream for an extra treat!"
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of a decadent chocolate dessert square topped with colorful sprinkles, served in a clean white ceramic plate on a light neutral surface. The rich texture of the chocolate and the vibrant colors of the sprinkles are highlighted, with a shallow depth of field and soft natural daylight creating gentle shadows. Sharp focus at the center of the dessert, captured at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>flour, sugar, cocoa powder, baking powder, salt, butter, eggs, vanilla extract, chocolate chips, sprinkles, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>task status failed: {'jobType': 'image', 'status': 'moderated', 'created': '2026-05-23T20:28:00.111Z', 'response': {'pinned': False, 'interaction_metadata': {'command_type': 1, 'authorizing_integration_owners': {'0': '0'</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523202/a0a1b5616dd.png</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/dfd556443ee.png</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/8df36d97176.png</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/7f73091269a.png</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/5d942637379.png</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trending Dessert You Can Make at Home</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
         <is>
           <t>Chocolate Avocado Mousse 🍫🥑
 Ingredients:
@@ -1689,12 +1291,12 @@
 Calories: ~250 per serving</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2026-05-23 16:47:24</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>{
   "name": "Chocolate Avocado Mousse",
@@ -1759,86 +1361,84 @@
 }</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Realistic, appetizing ULTRA close-up of a creamy chocolate avocado mousse served in a clean white ceramic bowl, garnished with fresh berries on top, on a light neutral surface. The mousse should fill 90–100% of the frame, showcasing its smooth texture, with a shallow depth of field and soft natural daylight creating gentle shadows. Sharp focus at the center of the mousse, presented at a slight 3/4 angle. Exclude people, hands, faces, text, logos, and packaging. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>avocados, cocoa powder, maple syrup, almond milk, vanilla extract, salt, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0523174/3139609e02f.png</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523174/1bcd501d7ba.png</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523174/609f77b33c1.png</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523174/3d1de3eab2c.png</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523174/6c4fee1feda.png</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/76370837a0b.png</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/0e2b9c77838.png</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/d73dc322bc5.png</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/11e52b0ec95.png</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523174/4bcd96f349f.png</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Viral Sweet Treat Everyone Loves</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Viral Sweet Treat Everyone Loves 🍰✨
 Ingredients:
@@ -1871,12 +1471,12 @@
 Calories: ~210 per serving</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2026-05-23 16:47:28</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>{
   "name": "Viral Sweet Treat Everyone Loves",
@@ -1962,86 +1562,84 @@
 }</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Realistic, appetizing ULTRA close-up of a freshly baked chocolate brownie square topped with vibrant rainbow sprinkles, served in a clean white ceramic plate, on a light neutral surface. The brownie has a rich, fudgy texture with melted chocolate chips visible, and the sprinkles add a pop of color. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the brownie center, slight 3/4 or eye-level angle. Exclude people, hands, faces, text, logos, and packaging. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>flour, sugar, cocoa powder, butter, eggs, vanilla extract, baking powder, salt, chocolate chips, rainbow sprinkles, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0523175/bfb22d66ca1.png</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/6d28deb28b4.png</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/222db64283a.png</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/8e096720c55.png</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/0e8eb361ad0.png</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523175/bd6c2671949.png</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/8126745f25a.png</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/fcff3025feb.png</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/c5229fa8be2.png</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/018c37d35bb.png</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Easy Dessert Going Viral Right Now</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Viral Chocolate Lava Mug Cake 🍫🔥
 Ingredients:
@@ -2070,12 +1668,12 @@
 Calories: ~350 per serving</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2026-05-23 16:47:34</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>{
   "name": "Viral Chocolate Lava Mug Cake",
@@ -2150,265 +1748,76 @@
 }</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Realistic, appetizing ULTRA close-up of a chocolate lava mug cake in a clean white ceramic mug, showcasing the molten chocolate center oozing out, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at food center, slight 3/4 or eye-level angle. Exclude people, hands, faces, text, logos, and packaging. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>flour, sugar, cocoa powder, baking powder, milk, vegetable oil, vanilla extract, chocolate, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0523175/9607e4e517b.png</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/dbedf3dde54.png</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/59e4e7f217d.png</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/8e37bd594d0.png</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0523175/dcd8c3823d2.png</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523175/dedbe9a194c.png</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/b6d60a90e4d.png</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/a1b9ed9a744.png</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/f12b56474b3.png</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523175/45522b2df5a.png</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Dessert That Everyone Is Saving</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Dessert That Everyone Is Saving 🍰✨
-Ingredients:
-- 1 ½ cups all-purpose flour
-- 1 cup granulated sugar
-- ½ cup unsweetened cocoa powder
-- 1 teaspoon baking powder
-- ½ teaspoon salt
-- ½ cup unsalted butter, melted
-- 2 large eggs
-- 1 teaspoon vanilla extract
-- 1 cup chocolate chips
-- ½ cup chopped walnuts (optional)
-Instructions:
-1. Preheat your oven to 350°F (175°C) and grease an 8x8 inch baking dish.
-2. In a large mixing bowl, whisk together the flour, sugar, cocoa powder, baking powder, and salt until well combined.
-3. In another bowl, mix the melted butter, eggs, and vanilla extract until smooth.
-4. Pour the wet ingredients into the dry ingredients and stir until just combined.
-5. Fold in the chocolate chips and walnuts if using.
-6. Spread the batter evenly into the prepared baking dish.
-7. Bake for 25-30 minutes, or until a toothpick inserted into the center comes out with a few moist crumbs.
-8. Allow to cool in the pan for 10 minutes before transferring to a wire rack to cool completely.
-9. Cut into squares and serve warm or at room temperature.
-Prep Time: 10 minutes
-Cook Time: 30 minutes
-Total Time: 40 minutes
-Course: Dessert
-Cuisine: American
-Servings: 16 squares
-Calories: ~200 per square</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-05-23 16:47:42</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>{
-  "name": "Dessert That Everyone Is Saving",
-  "summary": "This delicious dessert combines rich chocolate flavors with a hint of nuttiness from walnuts. Perfect for sharing, it's sure to be a hit at any gathering.",
-  "servings": "16",
-  "prep_time": "10",
-  "cook_time": "30",
-  "total_time": "40",
-  "calories": "200",
-  "course": "Dessert",
-  "cuisine": "American",
-  "keywords": [
-    "chocolate",
-    "dessert",
-    "easy",
-    "baking",
-    "squares"
-  ],
-  "notes": "Serve warm or at room temperature for the best taste. Calories are per square.",
-  "ingredients": [
-    {
-      "amount": "1 ½",
-      "unit": "cups",
-      "name": "all-purpose flour"
-    },
-    {
-      "amount": "1",
-      "unit": "cups",
-      "name": "granulated sugar"
-    },
-    {
-      "amount": "½",
-      "unit": "cups",
-      "name": "unsweetened cocoa powder"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "baking powder"
-    },
-    {
-      "amount": "½",
-      "unit": "teaspoon",
-      "name": "salt"
-    },
-    {
-      "amount": "½",
-      "unit": "cups",
-      "name": "unsalted butter, melted"
-    },
-    {
-      "amount": "2",
-      "unit": "large",
-      "name": "eggs"
-    },
-    {
-      "amount": "1",
-      "unit": "teaspoon",
-      "name": "vanilla extract"
-    },
-    {
-      "amount": "1",
-      "unit": "cups",
-      "name": "chocolate chips"
-    },
-    {
-      "amount": "½",
-      "unit": "cups",
-      "name": "chopped walnuts (optional)"
-    }
-  ],
-  "instructions": [
-    "Preheat your oven to 350°F (175°C) and grease an 8x8 inch baking dish.",
-    "In a large mixing bowl, whisk together the flour, sugar, cocoa powder, baking powder, and salt until well combined.",
-    "In another bowl, mix the melted butter, eggs, and vanilla extract until smooth.",
-    "Pour the wet ingredients into the dry ingredients and stir until just combined.",
-    "Fold in the chocolate chips and walnuts if using.",
-    "Spread the batter evenly into the prepared baking dish.",
-    "Bake for 25-30 minutes, or until a toothpick inserted into the center comes out with a few moist crumbs.",
-    "Allow to cool in the pan for 10 minutes before transferring to a wire rack to cool completely.",
-    "Cut into squares and serve warm or at room temperature."
-  ]
-}</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Realistic, appetizing ULTRA close-up of a decadent chocolate brownie served in a clean white ceramic plate, showcasing a rich, fudgy texture topped with melted chocolate chips and a sprinkle of chopped walnuts, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the brownie center, slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>flour, sugar, cocoa powder, baking powder, salt, butter, eggs, vanilla extract, chocolate chips, walnuts, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>task status failed: {'jobid': 'j0523202806300981179i-u2135-c1441888792192618647-bot:midjourney', 'jobType': 'image', 'status': 'moderated', 'created': '2026-05-23T20:28:06.468Z', 'request': {'channel': '14418887921926186</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523202/7db6bbd646a.png</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/5d3f4b0492c.png</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/ad721fdf91b.png</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/8d2131407c7.png</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0523202/b57273e88da.png</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T8"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,86 @@
       <c r="T1" s="1" t="inlineStr">
         <is>
           <t>error_ing</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Statut Article</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>article_title</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_article</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_title</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>recipe_title_pin</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_description</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_keywords</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_focus_keyword</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_description</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>rank_math_pillar_content</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pinterest_image</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>post_url</t>
         </is>
       </c>
     </row>
@@ -679,6 +759,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523170/9b31c98a8d0.png</t>
@@ -707,6 +788,166 @@
       <c r="S2" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Viral No-Bake Oreo Chocolate Dessert
+## Introduction
+The viral dessert sensation taking social media by storm combines simplicity with indulgence, offering a deliciously sweet escape for dessert lovers everywhere. This no-bake treat features layers of rich flavors and delightful textures, making it a perfect addition to any gathering or celebration. With just a few straightforward ingredients and minimal prep time, you'll soon discover why this dessert has captured the hearts and taste buds of so many.
+Imagine hosting a gathering with friends or family and revealing a visually stunning dessert that requires little effort to create. This particular dessert showcases layers of creamy mixture adorned with crunchy bits of Oreos and chocolate. It not only looks appealing but also brings a delightful blend of flavors that everyone will love. As a sweet treat, it caters to various tastes, making it a go-to dish for all types of occasions, from summer picnics to cozy family dinners.
+With the convenience of a no-bake recipe, this dessert shines particularly bright in the hot summer months, providing a refreshing end to any meal without heating up your kitchen. Its charm lies in the easy assembly and the blissful combinations of textures that dance harmoniously with each spoonful. Whether you’re planning a birthday party, a holiday gathering, or simply want to spoil yourself, this dessert is your ticket to culinary success.
+## Recipe Overview
+- Prep Time: 15 minutes  
+- Cook Time: 0 minutes  
+- Total Time: 4 hours 15 minutes  
+- Course: Dessert  
+- Cuisine: American  
+- Servings: 9  
+- Calories: ~250 per serving  
+This dessert offers a delightful blend of creamy, crunchy, and chocolatey components that come together in a visually appealing presentation. It's perfect for anyone looking for an easy and scrumptious dessert to whip up without turning on the oven. The combination of heavy cream, sweetened condensed milk, and whipped topping creates a smooth and decadent base, while crushed Oreos and mini chocolate chips add the perfect touch of texture and sweetness.
+## Ingredients
+- Heavy cream  
+- Sweetened condensed milk  
+- Vanilla extract  
+- Crushed Oreos  
+- Mini chocolate chips  
+- Whipped topping  
+- Fresh berries (for garnish)
+{{image_ing_1}}
+## Instructions
+1. In a large mixing bowl, combine the heavy cream, sweetened condensed milk, and vanilla extract.
+2. Using an electric mixer, whip the mixture until soft peaks form.
+3. Gently fold in the crushed Oreos and mini chocolate chips until evenly distributed.
+4. In a separate bowl, fold the whipped topping into the Oreo mixture until fully combined.
+5. Transfer the mixture into a 9x9 inch baking dish, spreading it evenly.
+6. Cover the dish with plastic wrap and freeze for at least 4 hours or until firm.
+7. Once set, cut into squares and garnish with fresh berries before serving.
+## The Allure of No-Bake Desserts
+### Convenience Factor
+No-bake desserts offer an easy solution for those who may not have baking skills or equipment. This recipe demonstrates how simple procedures can yield impressive results without the need for time-consuming baking. Since this dessert is devoid of complicated baking instructions, it empowers even novice cooks to create something spectacular. The ease of combining ingredients and allowing them to chill produces an impressive treat that feels far more labor-intensive than it actually is.
+### Ideal for Hot Weather
+In warmer months, no-bake desserts provide a refreshing option that doesn’t heat up your kitchen. The recipe in question, a delightful combination of creamy fillings and crunchy toppings, is especially suitable for summertime enjoyment. Treating your guests to this chilled dessert means they can savor something sweet without feeling weighed down by heavy pastries or custards. The lightness of the cream coupled with the refreshing hint of berries makes it a perfect match for those sunny afternoons.
+### Time-Saving Benefits
+With a prep time of just 15 minutes, this recipe is perfect for a last-minute dessert need. The long chill time only requires you to set it in the freezer, allowing you to focus on other aspects of your gathering. There’s something reassuring about being able to prepare a stunning dessert with such minimal time investment. Whether you’re unexpectedly hosting guests or need a dish for a last-minute potluck, this recipe easily fits within a busy schedule. Simply whip it up, place it in the freezer, and let it work its magic, freeing you to concentrate on other preparations.
+## Step-by-Step Preparation
+### Combining Ingredients
+Begin by gathering the primary ingredients which include heavy cream, sweetened condensed milk, and vanilla extract. This combination will serve as the creamy base of the dessert. Measuring out these ingredients and bringing them to room temperature can enhance the mixing process, allowing the components to blend smoothly without any lumps. It's essential to use a large mixing bowl to prevent any splattering as you whip the ingredients together.
+### Whipping the Cream Mixture
+Utilizing an electric mixer makes it easy to achieve soft peaks in your cream mixture. This step is crucial, as it gives the dessert a light and airy texture. Whipping the mixture until soft peaks are reached is a pivotal stage, ensuring that the final dessert maintains a fluffy consistency. Be cautious not to overwhip, as that can lead to a butter-like texture instead of the desired softness. The visual cue here is when the cream holds its shape but still appears glossy and lush.
+### Incorporating Texture
+Adding crushed Oreos and mini chocolate chips introduces delightful crunch and sweetness. Ensure these elements are evenly distributed throughout the mixture for consistent flavor in every bite. The huskiness of the crushed Oreos brings depth to the dessert, and the mini chocolate chips contribute bursts of rich chocolate flavor. Take your time during this step to fold the ingredients gently without deflating the whipped cream. The key is to ensure that the Oreo chunks and chocolate chips are well distributed, which enhances the overall tasting experience.
+### Final Mixing with Whipped Topping
+Folding in whipped topping should be done gently to maintain the lightness of the mixture. This step integrates the creamy elements while ensuring a fluffy finish. The whipped topping adds an extra layer of creaminess to the dessert, creating a beautiful balance with the richness of the sweetened condensed milk and the airy texture of the whipped cream. A gentle folding motion, rather than vigorous stirring, helps keep all the air you’ve whipped into the cream intact, resulting in a dessert that feels almost ethereal.
+## Freezing and Setting
+### Preparing the Baking Dish
+Selecting a suitable 9x9 inch baking dish is essential for proper setting. A lined or lightly greased dish ensures easy removal post-freezing. Once you have mixed all the components, carefully transfer the dessert mixture into the baking dish. Use a spatula to spread it evenly across the base and corners of the dish, ensuring there are no air pockets. This attention to detail is pivotal as it allows the dessert to freeze uniformly, so each piece is evenly set and easy to serve when the time comes.
+### Freezing Instructions
+Covering the dish with plastic wrap is an essential step that provides a barrier against any unwanted freezer odors, allowing the dessert to maintain its intended flavor. This protective layer ensures that the creaminess of the dessert is preserved while it freezes. The required freezing time of at least 4 hours is not only crucial for achieving a firm texture but also beneficial for the flavors to meld into one another thoroughly. By allowing sufficient time in the freezer, the delightful combination of cream, sweetened condensed milk, and crushed Oreos will create a deliciously decadent treat that holds together perfectly when served.
+### Tips for Optimal Freezing
+For the best results when freezing your dessert, ensure that your freezer is set at the correct temperature, typically around 0°F (-18°C). Maintaining a consistent chill is vital in achieving the desired texture. It’s advisable to avoid opening the freezer door frequently during the freezing process, as doing so can introduce warmer air, potentially affecting the firmness of your dessert. Additionally, placing the dish towards the back of the freezer can offer a more stable temperature, as this area tends to remain colder than the front.
+## Garnishing for Presentation
+### Choosing Fresh Berries
+Selecting ripe, fresh berries plays a vital role in enhancing both the aesthetic appeal and taste of your dessert. Strawberries, blueberries, and raspberries not only add bright pops of color but also provide a refreshing contrast to the rich and creamy base. When choosing your berries, look for ones that are vibrant, firm, and free from blemishes for the best results. Rinse them gently and pat dry to avoid excess moisture that can affect presentation.
+### Decorating Techniques
+Final garnishing with fresh berries not only elevates the visual appeal but also adds a touch of elegance to your dessert. Strategically placing berries on top of the squares just before serving creates an inviting and festive look. Consider arranging them in a pattern or grouping them to draw attention to the dessert's design. The combination of the dessert's rich chocolatey tones and the vibrant colors of the berries will certainly make for an eye-catching presentation, ideal for gatherings and special occasions.
+### Serving Suggestions
+To enhance the overall experience, consider pairing this dessert with additional complementary treats. A fresh mint sprig can provide an aromatic garnish that not only looks appealing but also adds a crisp, refreshing flavor. Drizzling with chocolate sauce or warm caramel can elevate the dessert further, offering a rich finishing touch that pleases the palate. This dessert is versatile enough to shine on its own, but a few thoughtful additions can take your serving to the next level.
+## Healthier Substitutions
+### Low-Fat Alternatives
+For those who wish to indulge without compromising on health goals, utilizing low-fat alternatives can significantly reduce calorie content while preserving flavor. Low-fat cream and reduced-sugar sweetened condensed milk are great substitutes that maintain the dessert's beloved creamy texture. These alternatives help you enjoy a guilt-free version of this mouthwatering treat while still offering the enjoyable experience of indulging in a delicious dessert.
+### Option for Dairy-Free
+Those with dietary restrictions can delight in this dessert too. By substituting heavy cream with coconut cream and using dairy-free whipped topping, you can create a delectable dairy-free version that still captivates the senses. These alternatives not only cater to lactose intolerance or dairy allergies but also lend a subtly different flavor that can enhance the overall experience with a hint of tropical essence.
+### Sweetness Level Adjustments
+For anyone wishing for a less sweet take on this dessert, it’s easy to adjust the sweetness level to fit personal preference. Consider reducing the amount of sweetened condensed milk, which can significantly lower overall sweetness while still providing richness. Additionally, mixing in unsweetened cocoa powder creates a delightful chocolate flavor that balances the sweetness for a more sophisticated profile, appealing to chocolate lovers who appreciate a more complex taste experience.
+## Storing Leftovers
+### Optimal Storage Methods
+To maintain the freshness and quality of leftover portions, it’s important to use airtight containers for storage. This prevents freezer burn and keeps the dessert tasting as fresh as possible. Make sure to allow the dessert to cool completely before sealing it in an airtight container for optimal results. It also helps if you label the container with the date it was made, ensuring you keep track of how long it has been stored.
+### Re-Freezing Considerations
+Although it’s possible to re-freeze any leftover dessert, it is generally recommended to enjoy it fresh for the best taste and texture. Repeated freezing and thawing can result in a change in consistency and flavor, which may be less pleasant. For the most enjoyable experience, savor within a reasonable timeframe after initially preparing it.
+### Shelf Life
+The dessert can last for a couple of weeks in the freezer, allowing for multiple servings over time. However, for the best combination of flavor and texture, it is advised to consume within the first week if possible. As with many desserts, the sooner you enjoy it after making, the fresher and more delightful it will taste.
+## Flavor Pairings
+### Complementary Beverages
+Pairing this decadent dessert with a perfect beverage can elevate the dining experience. A rich cup of coffee can balance the sweetness and enhance the flavors of chocolate and cream. Likewise, serving it alongside a light tea can cleanse the palate and offer a refreshing contrast. Dairy-free chocolate milk, for those inclined, serves as a luxurious companion that complements the chocolate elements beautifully, ensuring an indulgent experience.
+### Accompanying Treats
+To create a delightful dessert spread, consider offering additional treats such as brownies or fruit tarts. This variety not only caters to different tastes but also enhances the overall experience for your guests. The combination of different textures and flavors creates a more engaging dessert table that everyone will enjoy.
+### Seasonal Strengths
+This dessert shines particularly well during warm weather or festive occasions, making it an excellent choice for summer gatherings, holidays, or birthday parties. Its light and cool nature serves as a lovely contrast to the heat, while the inclusion of fresh berries can reflect seasonal flavors. Its versatility means it can now be enjoyed throughout the year, adapting to various themes and celebrations with ease.
+In summary, this viral dessert not only pleases the eye but also delights the palate with its rich, creamy layers complemented by the exciting crunch of Oreos and chocolate. Whether served at a gathering, family event, or as a special treat for yourself, its delightful flavors and ease of preparation make it a noteworthy addition to any dessert menu.
+</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Viral No-Bake Oreo Chocolate Dessert</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>No-Bake Oreo Chocolate Chip Dessert Recipe with Fresh Berries</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>Oreo Chocolate Chip Ice Cream Squares</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Indulge in this delicious no-bake Oreo chocolate chip dessert recipe, perfect for summer gatherings or a sweet treat at home. Featuring layers of creamy goodness and fresh berries, this viral dessert combines the rich flavors of chocolate chips and classic Oreo cookies for an unforgettable treat. Enjoy easy recipes that make summer entertaining a breeze while satisfying your sweet tooth.</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Viral dessert, Oreo dessert, easy recipes, chocolate chips, no-bake, summer treats</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Oreo Dessert Recipe</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Discover the viral dessert everyone is making now! Easy, no-bake recipe with Oreos, chocolate chips, and whipped topping.</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_1.jpg</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/viral-no-bake-oreo-chocolate-dessert/</t>
         </is>
       </c>
     </row>
@@ -855,6 +1096,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523170/49fae17ec8f.png</t>
@@ -883,6 +1125,169 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy TikTok Dessert You Must Try
+## Introduction
+This easy TikTok dessert is a delightful, no-bake treat that has quickly become a favorite among dessert enthusiasts. With its rich layers, fresh berries, and silky cream texture, this dessert not only looks stunning but is incredibly simple to prepare. Ideal for gatherings or a sweet indulgence at home, it's perfect for anyone who loves a quick yet impressive dessert. The layered presentation makes it not only a feast for the taste buds but for the eyes as well.
+Many people find themselves reaching for quick and delicious desserts, especially when time is of the essence. This TikTok dessert is an exemplary choice. It allows you to whip up something extraordinary without spending hours in the kitchen. The simplicity of the recipe really makes it accessible for dessert lovers of all skill levels. Whether you are preparing for a summer barbecue, a casual family dinner, or simply want a delightful treat to share with friends, this dessert promises to be a showstopper on any occasion.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 0 minutes
+- Total Time: 4 hours 15 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 6
+- Calories: ~250 per serving
+This dessert takes only 15 minutes of active preparation time, making it a fantastic option for busy individuals or families. The key to its success lies in the combination of whipped cream, sweetened condensed milk, and colorful mixed berries, beautifully layered between crushed graham crackers. With a total time of 4 hours and 15 minutes, which includes refrigeration, this dish allows flavors to meld, ensuring a rich tasting experience for all.
+## Ingredients
+### The following ingredients are essential for creating this delicious TikTok dessert:
+- 1 cup heavy cream
+- 1 cup sweetened condensed milk
+- 1 teaspoon vanilla extract
+- 1 cup crushed graham crackers
+- 1 cup mixed berries (strawberries, blueberries, raspberries)
+- Fresh mint leaves for garnish
+{{image_ing_1}}
+## Instructions
+1. In a large mixing bowl, whip the heavy cream until soft peaks form.
+2. Gently fold in the sweetened condensed milk and vanilla extract until combined.
+3. In a separate bowl, layer half of the crushed graham crackers at the bottom.
+4. Spread half of the cream mixture over the graham crackers.
+5. Add a layer of mixed berries on top of the cream mixture.
+6. Repeat the layers with the remaining graham crackers, cream mixture, and berries.
+7. Cover the dessert with plastic wrap and refrigerate for at least 4 hours, or overnight for best results.
+8. Before serving, garnish with fresh mint leaves.
+## Preparation Steps
+The preparation is straightforward and manageable, even for novice cooks. 
+### Whipping the Cream
+The first step to creating this indulgent dessert involves perfectly whipping the heavy cream. Using a large mixing bowl and an electric mixer or a hand whisk, beat the cream until soft peaks form. This process is critical as it creates the fluffiness that will lend a light texture to the dessert. Be careful not to over-whip the cream, as it can turn grainy or become butter if beaten too long.
+### Combining Ingredients
+Once your heavy cream has reached the desired fluffiness, it’s time to add sweetness and flavor. Gently fold the sweetened condensed milk into the whipped cream. Take your time with this step; folding preserves the air you've just beaten into the cream. Then, include the vanilla extract in the mix and ensure it blends well, maintaining the light and airy consistency. The sweetened condensed milk adds a rich sweetness, while the vanilla offers subtle aromatic notes.
+### Layering the Dessert
+Now that your cream mixture is ready, it’s time to create the layers that will define this dessert. Prepare a separate bowl for layering. Start with half of the crushed graham crackers, creating a solid base at the bottom. The crunch from the graham crackers provides a beautiful contrast to the creamy layers above. Follow this with half of the cream mixture spread evenly over the graham cracker layer. 
+### Adding Mixed Berries
+Next, add a colorful layer of mixed berries on top of the cream mixture. The combination of strawberries, blueberries, and raspberries not only adds visual appeal but also delivers bursts of tartness, balancing out the sweetness of the cream and mothered by the graham crackers. This is a fun assembly process, as every layer contributes to the overall texture and flavor, culminating in a beautiful dessert that beckons to be tasted.
+## Texture and Flavor Profile
+This dessert distinguishes itself through its contrasting textures and flavors, creating a delightful experience for the palate.
+### Creamy Layers
+The combination of whipped cream and sweetened condensed milk adds a sweet, creamy consistency that perfectly complements the crispiness of the graham crackers. Each bite delivers a delightful contrast that is satisfying and indulgent, offering a rich but light mouthfeel.
+### Fresh Berries
+The mixed berries introduce a delightful tartness and natural sweetness that cuts through the creaminess, creating a harmonious balance. This infusion of freshness makes the dessert exceptionally refreshing, especially in warmer months when you crave something light and sweet. The berries not only provide flavor but also excellent color, making it visually striking.
+## Serving Suggestions
+When it comes to serving this easy TikTok dessert, presentation can elevate its appeal. Plating it in individual cups or jars can create a more personalized touch, perfect for casual gatherings or formal events. Consider adding a dollop of whipped cream on top for extra softness and a sprinkle of additional crushed graham crackers for added texture. For a touch of elegance, you can also drizzle some berry coulis or chocolate sauce around the dessert. Fresh mint leaves placed strategically on each serving add both visual flair and a refreshing aroma, enhancing the overall dessert experience.
+### Individual Portions
+For a more elegant presentation, consider serving the dessert in small glass cups. This method not only enhances the visual appeal but also makes it easy for guests to partake. Layering the graham cracker, cream mixture, and mixed berries in clear cups allows everyone to appreciate the colorful hues and textures of the dessert. The clear glass highlights the beautiful progression of layers, inviting anticipation as guests can see the deliciousness waiting for them inside. 
+When serving in individual portions, you can adjust the serving size for customization; for instance, you might use smaller cups for an appetizer-size portion or larger ones for a generously satisfying dessert. Not only does this method elevate the overall dining experience, but it also helps to maintain portion control.
+### Family Style
+If you prefer a more relaxed atmosphere, family-style serving can create a warm, communal feel around the dining table. Place the entire dessert mixture back in the mixing bowl or a large serving dish, pausing only to admire its aesthetic appeal. This approach encourages sharing and conversation, allowing guests to help themselves, and adds a touch of hominess to any meal. 
+During family-style service, you could provide extra accessories on the side, like additional berries or whipped cream, encouraging everyone to personalize their dessert experience. This not only fosters togetherness but also keeps things casual, making it a perfect choice for gatherings or celebrations where interaction is key. 
+## Garnishing Tips
+Presentation is crucial in enhancing the overall appearance and appeal of your dessert. A few carefully chosen garnishes can go a long way in making this easy TikTok dessert look upscale and inviting.
+### Using Fresh Mint
+One of the simplest yet most effective ways to elevate the dessert’s appearance is by adding fresh mint leaves. Placing a few sprigs atop each serving not only provides a vibrant pop of color against the layers of cream and berries, but the aroma of fresh mint also adds an extra sensory delight. Mint’s freshness complements the sweetness of the berries, creating a delightful harmony in flavors. 
+For a refined presentation, consider placing the mint leaves at varying heights or arranging them artistically on the side. This small detail can transform your dessert from ordinary to extraordinary, leaving a lasting impression on guests.
+### Additional Toppings
+To further enhance the layers of flavor, consider using additional toppings. A scattering of extra mixed berries can create an inviting, abundant look, while a drizzle of chocolate sauce or caramel can add depth and richness. Not only do these toppings contribute to the visual appeal, but they also serve to elevate the taste experience. 
+To maximize texture, consider adding a sprinkle of crushed graham crackers on top for a delightful crunch. This added dimension can create a more layered experience, introducing a nice contrast to the creaminess of the dish.
+## Variations
+Feel free to experiment with different flavors and ingredients; this dessert is incredibly versatile, allowing for a unique spin on the classic recipe.
+### Flavor Additions
+For an added twist, infusing flavors can take this dessert to the next level. Almond extract provides a delightful nutty depth, while citrus zest can brighten the overall flavor profile. Consider experimenting with flavors that excite your palate or match the occasion. Adding a hint of citrus zest just before serving can offer a refreshing surprise that highlights the tartness of the berries.
+You could also try turning the dessert into a chocolate version by incorporating cocoa powder into the cream mixture or using chocolate graham crackers as the base instead of regular ones. These subtle shifts can create a whole new identity for the dessert while still retaining its beloved characteristics.
+### Fruit Swaps
+While mixed berries create a lovely balance of sweetness and tartness, other fruit options can vary the taste spectrum based on seasonal availability. Try swapping the mixed berries for peaches during summer, or consider using cherries for a juicy explosion of flavor. Each fruit brings its unique profile and can inspire distinctive adaptations of the original recipe.
+Additionally, bananas or even seasonal fruits like figs could add their charm to the dish. These substitutions not only make the dessert less predictable but also celebrate what’s in season, providing amazing flavor combinations.
+## Storage Recommendations
+Understanding how to store this dessert is crucial for maintaining its quality and ensuring it remains delectable. 
+### Refrigeration
+For best results, after assembling the dessert, cover it tightly with plastic wrap and refrigerate for at least 4 hours. For the optimum flavor and texture, allow the dessert to chill overnight. This resting period enables the flavors to meld beautifully and allows the graham crackers to soften perfectly, creating the desired creamy texture. 
+It is important that the dessert is stored in an airtight container or well-wrapped to prevent it from absorbing odors and staying fresh.
+### Shelf Life
+This dessert can last in the refrigerator for up to 2 days. However, while it may still be safe to consume beyond that time frame, freshness is key for maintaining the delightful taste and texture that makes this dessert so special. As time goes on, the berries may start to lose their vibrancy and texture, so it is recommended to enjoy the dessert within the first couple of days for the best experience.
+## Nutritional Information
+Understanding the nutritional aspects of the dessert can help in making informed choices while indulging in this treat.
+### Serving Size
+Each serving accommodates approximately 250 calories, making it a moderate indulgence. This calorie count is reasonable for a dessert, especially when compared to more traditional, calorie-laden options. 
+### Nutritional Benefits
+While the dessert features creamy richness from heavy cream, enjoyed in moderation, it can fit nicely into a balanced diet. The addition of mixed berries provides vitamins and antioxidants, contributing positively to the overall nutritional value. This balance of indulgence and refreshment ensures that the dessert is not just a delightful experience, but also a mindful choice.
+## Conclusion
+This easy TikTok dessert is a treat that strikes a perfect balance between rich creaminess and fruity freshness, making it an exciting addition to any dessert spread. With a mere 15 minutes of preparation time and a minimum refrigeration of four hours, this dessert is both convenient and delicious. Its beautiful layers and delightful taste ensure it will be a cherished recipe for any occasion.
+</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Easy TikTok Dessert You Must Try</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>No-Bake Mixed Berry Cream Dessert Recipe for Easy Summer Treats</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Berry Delightful No-Bake Parfait</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Indulge in this easy no-bake mixed berry cream dessert, perfect for summer gatherings. Bursting with fresh mixed berries and fluffy whipped cream, this delightful treat is a favorite among TikTok recipes. Enjoy a simple and refreshing way to satisfy your sweet tooth without turning on the oven this season.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>easy dessert, TikTok recipe, no-bake, mixed berries, summer treat, whipped cream</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Easy TikTok Dessert</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Discover this easy TikTok dessert recipe that combines cream, berries, and graham crackers for a delightful treat! 🍰✨</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_2.jpg</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-tiktok-dessert-you-must-try-7/</t>
         </is>
       </c>
     </row>
@@ -1027,6 +1432,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/62613ce40b0.png</t>
@@ -1055,6 +1461,149 @@
       <c r="S4" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Decadent Chocolate Avocado Mousse Recipe
+## Introduction
+The decadent chocolate avocado mousse is a delightful fusion dessert that redefines traditional sweetness with a creamy texture. Ideal for those looking to indulge without the guilt, this recipe harnesses the rich flavors of cocoa alongside the creamy goodness of ripe avocados. This mousse is not just easy to prepare but also offers a healthy twist to a classic treat, making it a perfect option for dessert lovers striving for a balanced lifestyle.
+Imagine spooning into a rich, velvety chocolate dessert that not only satisfies your sweet tooth but also provides essential nutrients. This mousse brings together the luscious properties of avocados and the indulgence of chocolate, transforming a simple ingredient list into a decadent dish. It’s a dessert that can be served at dinner parties, casual gatherings, or even enjoyed as a special treat during a self-care day.
+In a world where desserts are often laden with sugar and fats, this chocolate avocado mousse stands out. Its smooth texture and rich flavor offer a delightful experience, while being simple enough for even novice cooks to master. As summer approaches or during warm evenings, this no-cook option comes as a refreshing finale to any meal, leaving you and your guests wanting more.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 0 minutes
+- Total Time: 40 minutes
+- Course: Dessert
+- Cuisine: Fusion
+- Servings: 4
+- Calories: ~250 per serving 
+## Ingredients
+- 2 ripe avocados, peeled and pitted
+- 1/2 cup unsweetened cocoa powder
+- 1/4 cup maple syrup
+- 1/4 cup almond milk
+- 1 teaspoon vanilla extract
+- A pinch of sea salt
+{{image_ing_1}}
+## Instructions
+1. In a food processor, combine the ripe avocados, cocoa powder, maple syrup, almond milk, vanilla extract, and sea salt.
+2. Blend until the mixture is smooth and creamy, scraping down the sides as necessary.
+3. Taste the mousse and adjust sweetness if desired, adding more maple syrup if needed.
+4. Once fully blended, transfer the mousse into serving cups or bowls.
+5. Chill in the refrigerator for at least 30 minutes to firm up and enhance the flavors.
+6. Serve chilled, optionally topped with fresh berries or a dollop of whipped cream.
+## Texture and Consistency
+The creamy texture of the chocolate avocado mousse is one of the standout features of this dessert. By utilizing ripe avocados, you ensure that the mousse achieves a rich, smooth mouthfeel which is essential for any successful mousse. When combined with the cocoa powder and blended until completely smooth, the mousse develops an indulgent creaminess that mimics traditional chocolate desserts, enhancing the overall experience.
+Blending is a crucial step that directly impacts the mousse’s consistency. The food processor breaks down the avocados into a fine puree, which not only helps in incorporating all the ingredients but also creates an airy, light texture. If the mixture is not blended well, you may encounter lumps, which can distract from the silky smooth experience you would want in a mousse. Scraping down the sides of the processor ensures that all ingredients are perfectly amalgamated, yielding a flawless final product.
+The chilling time is equally important. A minimum of 30 minutes in the refrigerator allows the mousse to firm up, enhancing both its texture and flavor profile. This chill time allows for the flavors to meld beautifully while providing that desired thickness that elevates the overall dessert experience. Upon serving, you will find the mousse is not only cool and refreshing but also holds its shape perfectly in the cups.
+## Flavor Profile
+The flavor profile of this decadent chocolate avocado mousse is a harmonious blend that excites the palate. At its core, the chocolatey richness provided by the unsweetened cocoa powder steals the show. Cocoa powder is known for its deep, intense flavor, and in this recipe, it lends an exquisite chocolate flavor without the added sugars and fats that often accompany traditional chocolate desserts. Instead of relying on heavy cream or excessive sugar, the foundation of this mousse is built upon healthful ingredients, which is a significant draw for dessert lovers.
+Adding a layer of natural sweetness is the maple syrup, which contributes a gentle yet distinct flavor that balances the bitterness of the chocolate. Unlike refined sugars, maple syrup offers a unique, earthy sweetness that complements the other flavors beautifully without dominating them. This makes every bite of the mousse not just a sweet treat, but a complex interplay of flavors.
+Moreover, the avocado subtly enhances the taste and mouthfeel of the mousse. While it may not be immediately recognizable, the natural creaminess of the avocado rounds out the dessert, making it rich without feeling heavy. It ensures that every spoonful is decadent, offering a delightful combination of flavors that feels indulgent yet nutritious.
+For those who wish to amplify the flavor experience even further, adding toppings can bring this mousse to the next level. Fresh berries such as raspberries or strawberries provide a tart contrast to the rich base, while a dollop of whipped cream adds a layer of creaminess and a touch of sweetness that echoes the mousse's own flavors.
+This chocolate avocado mousse, with its complex flavor profile, rich texture, and stunning presentation, is sure to be a staple in your dessert repertoire. Whether you’re enjoying it watching a movie at home or serving it to guests at a dinner party, it captures the essence of fusion cuisine — merging health and indulgence in every delightful spoonful.
+## Serving Suggestions
+When it comes to serving your decadent chocolate avocado mousse, the choice of container can greatly enhance the overall presentation and experience of this fusion dessert. Elegant glass cups or bowls work beautifully, allowing the rich brown hue of the mousse to be visually appealing. Consider choosing clear glass to show off layers, especially if you opt for garnishes that add color.
+For a creative touch, you can layer the mousse with fresh fruits like berries or use smaller cups for individual servings at gatherings. Not only does this create an aesthetically pleasing display, but it also makes portion control easier for guests. 
+To elevate the presentation further, consider garnishing the mousse with fresh berries like raspberries or strawberries. The bright color of the fruit contrasts well with the dark chocolate mousse, adding an appealing visual dimension. A dollop of whipped cream on top, perhaps with a sprinkle of cocoa powder or crushed nuts, can provide an extra layer of decadence and whimsy. 
+## Nutritional Benefits
+The health benefits of avocados make them a standout ingredient in this mousse. Avocados are rich in healthy fats, particularly monounsaturated fats that promote heart health. They are also a good source of fiber, which aids in digestion, and packed with vitamins such as E, K, and several B vitamins, offering nutrients that contribute to overall wellness.
+Breaking down the nutritional components, the unsweetened cocoa powder is known for its high antioxidant content, which can help combat free radicals in the body. Maple syrup, while adding natural sweetness, comes with minerals like manganese and zinc. Almond milk provides a low-calorie, dairy-free option that has the advantage of being lactose-free as well. 
+When compared to traditional chocolate mousse that is often laden with heavy creams and refined sugars, this avocado-based version is a more health-conscious alternative. Each serving contains approximately 250 calories, showcasing how indulgence doesn’t have to come at the expense of health.
+## Fusion Cuisine Aspect
+The concept of fusion cuisine is beautifully exemplified in this chocolate avocado mousse. Fusion desserts blend elements from various culinary traditions, creating an innovative and delightful experience. This mousse incorporates classic elements of traditional chocolate mousse, such as the rich, chocolatey base while utilizing avocados, a staple of many health-focused modern cuisines.
+The use of avocado in dessert is an excellent illustration of how contemporary cooking is embracing healthier alternatives without sacrificing flavor. In many cultures, avocados are revered not only for their creamy texture but also for their versatility across both savory and sweet dishes. This dessert is a testament to how experimentation can yield exciting results in the kitchen.
+## Tips for Success
+When preparing this decadent chocolate avocado mousse, choosing the right avocados is critical to achieving the perfect texture. Look for ripe, creamy avocados that yield slightly when squeezed – this guarantees that they will blend smoothly and impart the desired richness to the mousse.
+To ensure a silky, smooth blend, make sure to use a reliable food processor. Scraping down the sides of the bowl during blending is essential, as it helps incorporate all the ingredients evenly. It’s best to taste and adjust the sweetness at the end; you might find that some avocados are naturally sweeter than others, and a quick additional drizzle of maple syrup can make a huge difference.
+Adjustments to sweet levels are also a part of personal preference. Make sure to sample the mixture before setting it in the refrigerator to enhance its flavor. This possibility for customization allows each dessert to be tailored to individual taste.
+## Common Questions
+### **Can I substitute any ingredients?**
+While this recipe is designed to maximize the health benefits and flavors of the selected ingredients, substitutions can be made if necessary. For instance, if maple syrup isn't available, agave nectar or honey (not vegan) could be alternatives, though these may introduce different flavor profiles.
+### **How to store leftover mousse?**
+Leftover mousse can be stored in an airtight container in the refrigerator for up to two days. Ensure that the mousse is covered well to prevent it from absorbing any flavors or odors from the fridge.
+### **What other toppings can I use besides berries and whipped cream?**
+Beyond berries and whipped cream, consider toppings like crushed nuts, coconut flakes, or even shaved dark chocolate for added texture and flavor. A drizzle of nut butter can provide a delicious contrast, while different fruits like banana slices or oranges can offer fresh notes.
+## Variations on the Recipe
+This chocolate avocado mousse can serve as a base for various creative variations. One delightful option is to incorporate spices or extracts such as cinnamon, nutmeg, or peppermint to create different flavor profiles. A teaspoon or two of coffee extract can also heighten the chocolate flavors beautifully.
+For those who enjoy crunch in their desserts, incorporating nuts such as crushed almonds, hazelnuts, or walnuts can add an appealing texture. Simply fold in finely chopped nuts after the mousse has been blended and before chilling.
+Additionally, experimenting with different plant-based milks can yield varying consistencies and flavors. Cashew milk, oat milk, or coconut milk can each bring their unique creaminess to your mousse, allowing for endless creativity in your kitchen.
+## Conclusion
+This chocolate avocado mousse stands out as a unique and indulgent dessert that harmoniously blends rich flavors with a creamy texture. With its quick preparation and chilling time, this fusion dish offers a delightful option for dessert enthusiasts seeking a healthy twist on a classic favorite. Each portion provides a satisfying experience while keeping within a reasonable calorie range, making it perfect for those moments when sweet cravings strike.
+</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Decadent Chocolate Avocado Mousse Recipe</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Creamy Chocolate Avocado Mousse Recipe: A Decadent Healthy Dessert</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Creamy Chocolate Avocado Delight</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Indulge in this creamy chocolate avocado mousse recipe, a decadent yet healthy dessert that satisfies your sweet cravings without the guilt. Perfect as a quick dessert for any occasion, this vegan chocolate treat is effortlessly made with ripe avocados and requires no baking. Enjoy a rich, luscious flavor that delights your taste buds while nourishing your body.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>chocolate mousse, avocado dessert, healthy dessert, vegan chocolate, no-bake recipe, quick dessert</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Chocolate Avocado Mousse</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Indulge in our decadent chocolate avocado mousse, a rich and creamy dessert that's vegan and full of flavor!</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_3.jpg</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/decadent-chocolate-avocado-mousse-recipe/</t>
         </is>
       </c>
     </row>
@@ -1228,6 +1777,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/fc5bd93be4b.png</t>
@@ -1256,6 +1806,177 @@
       <c r="S5" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy Viral Dessert You’ll Love
+## Introduction
+Exploring a simple yet delightful dessert that has captured the hearts of many, this easy viral dessert combines rich flavors with a quick preparation time. The harmonious blend of cocoa and sugar results in a cake that's perfect for any occasion. The appeal of this dessert lies in its simplicity and the indulgent chocolatey experience it offers.
+This cake is not just easy to make; it is also incredibly versatile. You can serve it at birthday parties, family gatherings, or as a delightful treat after dinner. The chocolate chips embedded within add chunks of gooey sweetness that elevate each bite. Not only is it pleasing to the palate, but it also requires minimal ingredients, making it an accessible choice for bakers of all skill levels. 
+Whether you are a seasoned chef or a novice in the kitchen, this recipe provides a straightforward approach to creating a mouthwatering dessert. With a little over thirty minutes, you can prepare a cake that looks and tastes as though it required hours of toil. This dessert is likely to become a cherished recipe that you'll turn to time and time again, bringing joy to both you and your loved ones.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 30 minutes
+- Total Time: 40 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 8
+- Calories: ~250 per serving
+## Ingredients
+- 1 cup all-purpose flour
+- 1/2 cup granulated sugar
+- 1/4 cup unsweetened cocoa powder
+- 1/2 teaspoon baking powder
+- 1/4 teaspoon salt
+- 1/2 cup milk
+- 1/4 cup vegetable oil
+- 1 teaspoon vanilla extract
+- 1/2 cup chocolate chips
+- Whipped cream for topping (optional)
+{{image_ing_1}}
+## Instructions
+1. Preheat your oven to 350°F (175°C) and grease a 9-inch round cake pan.
+2. In a large mixing bowl, combine the flour, sugar, cocoa powder, baking powder, and salt.
+3. In a separate bowl, whisk together the milk, vegetable oil, and vanilla extract until well combined.
+4. Pour the wet ingredients into the dry ingredients and mix until just combined.
+5. Fold in the chocolate chips gently into the batter.
+6. Pour the batter into the prepared cake pan and spread it evenly.
+7. Bake for 25-30 minutes or until a toothpick inserted in the center comes out clean.
+8. Let the cake cool in the pan for 10 minutes, then transfer to a wire rack to cool completely.
+9. Serve with whipped cream on top if desired.
+### Preheating the Oven
+The first essential step in this baking adventure is to preheat your oven to 350°F (175°C). Preheating is vital because it ensures that your cake will bake evenly from the moment it enters the oven. Having the oven at the correct temperature contributes to a light and fluffy texture. While waiting for the oven to heat up, you can prepare your baking pan. Greasing the 9-inch round cake pan is crucial to ensure that your cake comes out without sticking. A non-stick spray or a light coating of vegetable oil can do the trick. Having the right tools on hand will streamline the process: find a mixing bowl, a whisk, and measuring cups that are necessary for your ingredients.
+### Mixing Dry Ingredients
+In a large mixing bowl, you will combine the dry ingredients: all-purpose flour, granulated sugar, unsweetened cocoa powder, baking powder, and salt. Mixing these dry ingredients well is important for achieving a uniform cake. The role of baking powder is to act as a leavening agent, allowing the cake to rise during baking. Salt, on the other hand, enhances the flavors, balancing out the sweetness of the sugar and cocoa. It’s beneficial to whisk these components together thoroughly, ensuring there are no clumps and that every scoop of flour is well integrated. This even distribution of dry components is critical to the cake's overall texture and flavor.
+### Preparing Wet Ingredients
+Now that your dry ingredients are ready, it’s time to focus on the wet ingredients. In a separate bowl, whisk together the milk, vegetable oil, and vanilla extract until they are well combined. This step is essential to ensure that the oil is evenly spread throughout the batter, contributing to the cake's moistness and flavor. Here, every ingredient plays its part: milk adds richness, oil provides moisture, and vanilla extract introduces a warm, aromatic element to the dessert. Using a whisk enables you to achieve a smooth mixture that blends the flavors harmoniously, which is key to the delicate texture of your cake.
+### Combining Ingredients
+At this stage, you’re ready to merge the wet and dry mixtures. Pour the wet ingredients into the bowl containing the dry ingredients. Mix these together until just combined. Be careful not to overwork the batter, as this could lead to a denser cake. The technique here involves folding the ingredients together gently, which helps to maintain a light and airy structure. Finally, you will fold in the chocolate chips. This addition is what makes this dessert truly special; the melted chocolate chunks create pockets of gooey sweetness, enhancing every bite of the cake.
+### Baking the Cake
+After combining the ingredients, pour the batter into your prepared cake pan and spread it evenly. The evenness of your batter will help the cake bake uniformly. Place the pan in the preheated oven and set your timer for 25 to 30 minutes. During this time, the aroma from the baking cake will fill your kitchen, promising a delightful experience. To check for doneness, insert a toothpick into the center of the cake; when it comes out clean, the cake is ready. Keeping an eye on the baking duration is crucial to prevent over-baking, which could dry out the cake.
+### Cooling the Cake
+Once the baking time is complete, remove the cake from the oven and let it cool in the pan for about 10 minutes. This cooling time allows the cake to set, making it easier to transfer to a wire rack. Cooling on a rack is important because it permits air circulation around the cake, preventing condensation from forming on the bottom, which could otherwise lead to a soggy texture. Once cooled, you can enjoy serving this cake either plain or with whipped cream on top for an extra touch of decadence.
+This cake is now a blank canvas ready for you to customize, making each serving an occasion in itself.
+### Storage Instructions
+The delicious dessert can be enjoyed over several days if stored properly. Here are some best methods to ensure your cake remains fresh and flavorful over time:
+To maintain the cake's moistness, store any leftover slices in an airtight container at room temperature for up to two days. If you anticipate needing to keep it longer, refrigerating it is a sensible option. The cake can last in the refrigerator for around 3 to 5 days. Just remember to wrap it well with plastic wrap to prevent it from absorbing any refrigerator odors and to maintain its softness.
+For longer storage, consider freezing portions of the cake. Once completely cooled, wrap individual slices tightly in plastic wrap and place them in a freezer-safe bag. This method helps to keep the cake fresh for about three months. Whenever you crave a piece, simply thaw each slice in the refrigerator for a few hours or leave it at room temperature for quick enjoyment.
+## Nutritional Information
+### Caloric Content
+This dessert is not only quick to prepare but also offers a satisfying treat at approximately 250 calories per serving. The breakdown of the nutritional content mainly comes from the ingredients used, which create a balanced dessert.
+- **All-purpose flour** contributes carbohydrates and serves as the base.
+- **Granulated sugar** provides sweetness and energy.
+- **Cocoa powder** adds flavor while being relatively low in calories.
+- **Milk and vegetable oil** contribute fats and moisture, enhancing the cake's richness.
+- **Chocolate chips** are key for that melty, indulgent experience, adding both flavor and calories.
+Understanding the contribution from each ingredient can guide you in adjusting portion sizes and making informed choices about enjoying this delectable dessert.
+### Dietary Considerations
+Many bakers look for ways to modify recipes to meet dietary restrictions. For instance, if you're considering a vegan adaptation, you can substitute dairy milk with almond milk or coconut milk, and use a suitable egg replacer like flaxseed meal or applesauce. Swapping out vegetable oil for a plant-based butter alternative will maintain the dessert's texture.
+For those needing gluten-free options, a good quality gluten-free all-purpose flour can easily replace regular flour. Be sure to select a brand that has Xanthan gum included, as this will help mimic the structure typically provided by gluten.
+Considering dietary adaptations not only makes this dessert enjoyable for more people but can also enhance its healthfulness without sacrificing flavor.
+## Cultural Context
+### The Role of Desserts in American Cuisine
+Desserts hold a significant place in American cuisine, often acting as the centerpiece of celebrations and gatherings. They are an integral part of holiday meals, birthday parties, and other festive occasions, underscoring their importance in creating joyful memories and traditions.
+Historically, chocolate cakes have been cherished in American baking since the late 19th century, following the introduction of cocoa powder. This dessert not only reflects the nation’s sweet tooth but also showcases the ability to evolve with contemporary tastes. Today, the popularity of chocolate desserts continues, as they can be customized and adapted, allowing them to resonate with different generations and palates.
+### Popularity of Viral Recipes
+In recent years, viral recipes have taken the culinary world by storm, thanks to social media platforms like Instagram and TikTok. What makes a dessert go viral often boils down to its visual appeal, unique elements, and, more importantly, its simplicity. Recipes that promise minimal ingredients while still delivering great taste tend to capture attention.
+Social media’s influence can’t be underestimated; users share their baking successes (and failures) widely. The ease of replicating a recipe and sharing the process adds to the communal experience of cooking and baking. This easy viral dessert’s combination of familiar ingredients and straightforward instructions make it particularly attractive, leading to widespread sharing and experimentation in kitchens everywhere.
+## Variations of the Recipe
+### Flavor Customizations
+To create a unique twist on this cake, consider adding spices like cinnamon or a touch of espresso powder to enhance the chocolate flavor. Vanilla bean paste can also elevate the vanilla extract into an aromatic experience. For those wanting fruity notes, adding mashed bananas or pureed apples will result in a subtly flavored cake.
+Incorporating nuts like walnuts or pecans adds a delightful crunch. You could also try various fruits like cherries or raspberries, which complement the chocolate while adding a fresh touch. Alternative chocolate types, such as white chocolate or dark chocolate, can also be used to experiment with flavors.
+### Texture Modifications
+If you prefer a fudgier dessert, consider reducing the flour slightly or adding an extra tablespoon of oil for moisture. Alternatively, for a lighter, cakey texture, you could increase the baking powder by a few pinches. Techniques like beating the batter until just combined can influence the texture significantly, keeping it tender yet delightful.
+Baking time is crucial as well; checking for doneness earlier can prevent overbaking, which often leads to a drier cake. Adjusting baking time can be essential to achieving that perfect melt-in-your-mouth experience.
+### Seasonal Versions
+Adapting the recipe for different seasons is an enjoyable way to explore variations. Incorporate seasonal spices like nutmeg for autumn or peppermint extract for winter holidays. You could even use fresh berries in the summer for a refreshing twist, adding them as a filling between layers or as a topping.
+Presentation can also align with the seasons. In the fall, a cake decorated with caramel sauce and pecans feels festive, while a dusting of powdered sugar for a winter wonderland effect can captivate guests during the colder months.
+## Common Mistakes to Avoid
+### Ingredient Mishaps
+Accurate measuring is essential in baking, as deviations can lead to unfavorable results. Always level off dry ingredients for consistency, and be cautious with substitutions; some ingredients, like baking powder, have specific chemical roles that may not be replicable with alternatives.
+Using fresh ingredients immensely boosts flavor, so checking expiration dates on baking supplies is always a smart move.
+### Techniques to Perfect
+One crucial aspect of batter mixing is to avoid overmixing, which can toughen the final product. Look for a unified batter with a few lumps remaining; this signifies a delicate texture is on the way. Be attentive to timing as well; a toothpick coming out clean should guide you, but slight moisture can signal a perfectly baked cake.
+Cooling is equally essential: letting the cake sit too long in the pan may lead to a soggy bottom, so transferring it to a wire rack promptly is advisable.
+### Troubleshooting Baking Issues
+If your cake rises unevenly, it may be due to an unlevel oven rack or an incorrect oven temperature. Using oven thermometers can help ensure accurate temperatures; some ovens might not tell the complete truth.
+Cakes that stick to the pan can be avoided through thorough greasing or using parchment paper, which provides another layer of protection. In unfortunate cases of cake failure, a trifle can be created, layering broken cake pieces with whipped cream and fruit for redemption.
+## Conclusion
+This easy viral dessert strikes a perfect balance between rich flavors and simple preparation. With a moist texture and delicious chocolate taste, it serves as a delightful end to any meal. The quick cooking time makes it an ideal choice for both spontaneous gatherings and planned events, bringing joy to dessert enthusiasts.
+</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Easy Viral Dessert You’ll Love</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Delicious Easy Chocolate Cake Recipe You Need to Try Tonight</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Decadent Chocolate Chip Cake Delight</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Indulge in the ultimate comfort food with this delicious easy chocolate cake recipe, perfect for satisfying your sweet cravings tonight. This viral recipe is not only quick to make, but it pairs wonderfully with a dollop of whipped cream for an extra touch of decadence. Treat yourself and your loved ones to this delightful dessert that will make any occasion extra special.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>easy dessert, chocolate cake, viral recipe, baking, quick dessert, whipped cream</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Easy Viral Dessert</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Discover this easy viral dessert recipe that everyone will love! Indulge in a chocolate delight that's simple to make. 🍰✨</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_4.jpg</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-viral-dessert-youll-love-2/</t>
         </is>
       </c>
     </row>
@@ -1401,6 +2122,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523174/76370837a0b.png</t>
@@ -1429,6 +2151,168 @@
       <c r="S6" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy Chocolate Avocado Mousse Recipe
+## Introduction
+The pursuit of a delectable dessert is a journey every food lover embarks upon, and Chocolate Avocado Mousse offers a guilt-free indulgence that combines rich flavors with healthy ingredients. This creamy, chocolatey delight showcases the use of ripe avocados, proving that dessert can be nourishing and delicious at the same time. With a simple preparation process that requires no cooking, this recipe is perfect for anyone looking to satisfy their sweet tooth without compromising on health.
+Imagine the smooth texture of chocolate melting in your mouth, combined with the subtle creaminess of avocado. This dessert not only satisfies your cravings but also provides a unique twist that many haven't yet explored. It serves as an excellent option for dinner parties, holiday gatherings, or even a simple weeknight treat after dinner. With its luscious texture and rich flavors, this mousse will surprise and delight anyone who tries it, showing that healthy ingredients can truly shine in dessert.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 0 minutes
+- Total Time: 40 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 4
+- Calories: ~250 per serving
+## Ingredients
+- 2 ripe avocados, peeled and pitted
+- 1/2 cup unsweetened cocoa powder
+- 1/4 cup maple syrup
+- 1/4 cup almond milk
+- 1 teaspoon vanilla extract
+- Pinch of salt
+{{image_ing_1}}
+## Instructions
+1. In a food processor, combine the ripe avocados, cocoa powder, maple syrup, almond milk, vanilla extract, and a pinch of salt.
+2. Blend the ingredients until smooth and creamy, scraping down the sides as needed.
+3. Taste the mousse and adjust sweetness if necessary by adding more maple syrup.
+4. Once fully blended, transfer the mousse into serving bowls or cups.
+5. Refrigerate for at least 30 minutes to allow the flavors to meld and the mousse to set.
+6. Serve chilled, topped with fresh berries or a dollop of whipped cream if desired.
+## Health Benefits of Chocolate Avocado Mousse
+### Nutritional Value
+Avocados, often celebrated for their health benefits, form the backbone of this delightful mousse. They are rich in healthy monounsaturated fats, particularly oleic acid, which is known to support heart health. Packed with vitamins such as Vitamin K, E, and C, avocados also provide an array of essential nutrients and minerals, including potassium and magnesium. This nutritional powerhouse helps enhance skin health and provides a significant dose of dietary fiber, making this dessert not only a sweet treat but also a beneficial addition to your diet.
+Cocoa powder, the other star ingredient of this recipe, is equally impressive. It is renowned for its high antioxidant content, which can help combat oxidative stress in the body. These antioxidants, specifically flavonoids, have been linked to improved cardiovascular health and better brain function. Thus, combining the benefits of avocados and cocoa powder in this chocolate mousse creates a dessert that is as beneficial as it is indulgent.
+### Low Sugar Content
+One of the key components of this Chocolate Avocado Mousse is maple syrup, a natural sweetener that offers a healthier alternative to refined sugars. With a lower glycemic index than traditional sugar, maple syrup does not cause significant spikes in blood sugar levels, making it a suitable option for those mindful of their sugar intake. By using maple syrup, this dessert retains its sweetness without the drawbacks associated with refined sugar, which can lead to energy crashes and cravings.
+By opting for a dessert like this that uses natural sweeteners, you can enjoy a delicious treat while adhering to a healthier lifestyle. The incorporation of lower sugar content not only makes this mousse taste delightful but also aligns with the growing trend of reducing sugar intake in food preparation.
+### Dairy-Free Delight
+In today’s world, where many are exploring plant-based diets or managing lactose intolerance, the use of almond milk in this recipe proves particularly advantageous. Almond milk serves as a creamy base that complements the avocados while delivering a nutty flavor that enhances the overall dessert experience. Additionally, it is lower in calories compared to traditional dairy products and is an excellent source of Vitamin E, an important antioxidant for skin health.
+For those who follow a dairy-free diet, this Chocolate Avocado Mousse allows you to indulge in a dessert without feeling guilty or compromising on flavor. The mousse can be enjoyed by people of all dietary preference, showcasing how easy it is to cater to various nutritional needs without sacrificing taste.
+## Step-by-Step Preparation Process
+### Combining Ingredients
+Creating the perfect Chocolate Avocado Mousse begins with meticulously combining the ingredients. The first step involves gathering ripe avocados, unsweetened cocoa powder, maple syrup, almond milk, vanilla extract, and a pinch of salt in your food processor. The quality of each ingredient contributes significantly to the final product, so using ripe avocados is crucial. They should be soft to the touch but not overripe, as this ensures a smooth texture.
+Measuring the ingredients accurately during this initial step is paramount. Each component plays a unique role; the cocoa powder imparts rich chocolate flavors while the avocado provides creaminess and nutrition. The maple syrup adds sweetness without overpowering the dessert, and the almond milk achieves the desired consistency. Blending these ingredients correctly allows for a delightful mousse that is well balanced and smooth.
+### Blending to Perfection
+Once the ingredients are combined, it’s time to blend them to perfection. Use your food processor to mix the ingredients until the mousse reaches a silky smooth consistency. This is where the magic happens; the textures of avocado and cocoa harmonize, creating a rich chocolate base. Remember that scraping down the sides of the processor is important to ensure even blending. This technique helps avoid lumps and makes sure that every bit of avocado is incorporated into the mix.
+This step is crucial as the air introduced during blending contributes to the mousse's light and airy quality. Aim for a luscious texture that melts in your mouth, lifting the simple ingredients into a decadent dessert experience.
+### Taste Testing
+After achieving the desired smoothness, it’s essential to taste the mousse before serving. When likely becoming a staple dessert, you want to ensure that the sweetness is just right. If you find that it needs a bit more sweetness, carefully adjust by incorporating additional maple syrup. However, approach this step with caution—too much syrup can overshadow the rich chocolate flavor of the cocoa. 
+Perfecting the balance of sweetness is key to ensuring that your mousse remains a dessert that is enjoyed and remembered. The goal is to create a wonderfully chocolaty treat that resonates with chocolate lovers while still being a healthy alternative.
+### Creative ways to serve the mousse in various bowls or cups
+When presenting your Chocolate Avocado Mousse, the choice of serving dishes can dramatically enhance the overall experience. Utilize a variety of textures and shapes to make your dessert visually appealing. For individual servings, consider using clear glass cups or small mason jars that let the vibrant color of the mousse shine through. You can layer the mousse with toppings to create stunning visual contrasts that capture the eye.
+Additionally, unique bowls can elevate the presentation; think about using elegant dessert bowls, rustic ramekins, or even small wooden dishes for a touch of charm. For a more festive look, consider serving the mousse in hollowed-out fruits, such as oranges or coconuts, which adds a playful element to your dessert. Remember, the visual appeal is an essential part of the dessert experience, and thoughtful presentation can turn a simple recipe into a luxurious treat.
+### Decorative elements to enhance visual appeal
+To further enhance the visual appeal of your Chocolate Avocado Mousse, consider adding decorative elements that complement the dish. Edible flowers provide a pop of color and a touch of elegance, while mint leaves can add a fresh green contrast. Drizzling chocolate or berry sauce over the mousse before serving can create an eye-catching effect, and a dusting of cocoa powder or powdered sugar adds sophistication.
+If you’re using fresh berries as a topping, arrange them artfully on top for not just flavor but also stunning presentation. Incorporating textures like crushed nuts or coconut flakes can add both visual interest and an extra layer of flavor. These decorative elements not only improve the aesthetics of the dish but can also entice guests before they have even taken their first bite.
+### Topping Options
+Toppings are a delightful way to personalize your Chocolate Avocado Mousse and add different dimensions to flavor and texture. Fresh berries such as raspberries, strawberries, or blueberries are ideal for not only their vibrant colors but also their tartness, which contrasts beautifully with the rich, chocolatey mousse. The combination provides a burst of freshness that elevates the overall dessert experience.
+For those who enjoy creamy textures, a dollop of whipped cream is a classic choice. Whether using regular cream or a dairy-free alternative, this topping adds a lovely finish to the mousse. Alternatively, consider adding a sprinkle of toasted nuts, such as almonds or hazelnuts, that provide a satisfying crunch and nutty flavor, enhancing the richness of the mousse. Coconut flakes can offer a tropical twist, contributing both texture and flavor.
+### Pairing Beverages
+With its rich and creamy texture, the Chocolate Avocado Mousse pairs well with a variety of beverages that can enhance the enjoyment of this dessert. For those who prefer something classic, a glass of red wine, such as a Cabernet Sauvignon or a Merlot, can beautifully complement the deep flavors of the chocolate. A dessert wine, like a port, adds another layer of indulgence.
+For non-alcoholic options, consider serving a rich hot chocolate topped with whipped cream or perhaps a smooth, cold brew coffee that contrasts nicely with the sweetness of the mousse. Herbal teas, particularly those flavored with chocolate or mint, can also balance the richness and provide a soothing finish to the meal. Choosing beverages thoughtfully can transform your dessert into a well-rounded experience.
+## Storing Chocolate Avocado Mousse
+### Refrigeration Techniques
+Proper storage is essential for maintaining the quality of your Chocolate Avocado Mousse. Given that it contains ripe avocados, which can quickly oxidize, it’s crucial to store the mousse correctly. To keep it fresh, transfer the mousse into airtight containers. These containers help prevent air exposure that can lead to browning.
+When covering the mousse, ensure that the wrap or lid is tightly sealed to minimize oxidation. If you are using plastic wrap, press it directly onto the surface of the mousse before sealing the container; this technique will reduce the air gap and maintain its vibrant appearance. The mousse can typically be stored in the refrigerator for about 2 to 3 days, ensuring you enjoy its creamy texture and flavor.
+### Freezing for Later Use
+If you want to make your Chocolate Avocado Mousse in advance, freezing can be a convenient option. Scoop the mousse into freezer-safe containers, leaving a little space at the top to allow for expansion as it freezes. You can freeze the mousse for up to 1 month without compromising its taste too much.
+When it’s time to eat, remove the mousse from the freezer and let it thaw in the refrigerator for several hours or overnight. This gradual thawing helps to maintain the texture and taste. Once thawed, stir gently to incorporate any separation that may have occurred. The mousse may not be as smooth as when freshly made, but it will still retain its rich flavor.
+## Variations of Chocolate Avocado Mousse
+### Health-Conscious Twists
+For those looking to customize their Chocolate Avocado Mousse to align with specific dietary preferences, there are a variety of health-conscious twists. Alternative sweeteners like agave nectar or honey can replace maple syrup, catering to personal taste or dietary restrictions. These substitutes can still provide the necessary sweetness while potentially offering different flavor profiles.
+For an added nutritional boost, consider incorporating superfoods like chia seeds or hemp hearts. These ingredients not only enhance the health benefits of the mousse but also add a delightful texture. Chia seeds, in particular, can create a slightly thicker consistency and introduce additional fiber and omega-3 fatty acids, making the dessert even more nourishing.
+### Flavor Enhancements
+Introducing new flavors to your Chocolate Avocado Mousse can take the dessert to new heights. Infusions of different flavors such as peppermint extract or a splash of orange zest can provide a refreshing twist that complements the chocolate beautifully. A pinch of cinnamon can also deepen the flavor profile, adding warmth and a subtle aromatic note.
+Exploring spices and extracts allows for creativity while enhancing the dessert’s richness without overwhelming it. The key is to add just enough to enhance the existing flavors without overpowering the main ingredients, making each bite uniquely enjoyable.
+### Vegan and Allergy-Friendly Adaptations
+Making your Chocolate Avocado Mousse accommodating for different dietary needs can be achieved with simple ingredient substitutions. To create a nut-free version, you can swap out almond milk for a soy-based or coconut milk alternative, ensuring the mousse remains creamy without compromising on flavor.
+Keeping the mousse fully vegan-friendly can be easily achieved as well, since all the ingredients used are plant-based. If any guests have soy allergies, it’s easy to replace soy products with coconut or rice alternatives. Being mindful of dietary restrictions allows everyone to indulge in this delightful dessert without worry.
+## Cultural Influences on Dessert Recipes
+### Evolution of Chocolate Desserts
+The history of chocolate desserts in American cuisine reveals a rich tapestry of flavors and inspirations. Chocolate, once a luxurious ingredient primarily enjoyed in beverages, has evolved into a beloved element found in various desserts. American bakers have transformed chocolate into countless styles, from cakes and brownies to mousse, each interpretation becoming a unique expression of culture and taste.
+The incorporation of ingredients like avocado into dessert recipes highlights contemporary culinary trends focused on health and sustainability. As consumers grow more conscious of their dietary choices, recipes evolve to include more nutritious options without sacrificing indulgence.
+### Health Trends in Dessert Making
+The rise of health-conscious dessert recipes reflects broader cultural shifts toward healthier lifestyles. As people become more aware of the effects of sugar, preservatives, and artificial ingredients, there is a growing demand for desserts that focus on natural, wholesome components. Chocolate Avocado Mousse serves as a prime example of how desserts can be reimagined to satisfy cravings while also aligning with those health-conscious choices.
+The connection between cultural shifts and the demand for healthier dessert options fosters diversity in culinary traditions, ensuring that desserts can be both satisfying and nutritious. This influences the way we approach sweets today, paving the way for innovative recipes that cater to modern dietary preferences.
+## Conclusion
+Chocolate Avocado Mousse emerges as a rich, creamy dessert that delights the palate while promoting health. With a total time of just 40 minutes and the ability to serve up to four, this American dessert is not only easy to make but also fulfilling. Enjoy the harmonious blend of flavors that satisfy your sweet cravings without the guilt.
+</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Easy Chocolate Avocado Mousse Recipe</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Creamy Chocolate Avocado Mousse: Easy, Healthy Dessert Recipe</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Decadent Chocolate Avocado Delight</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Indulge in a creamy chocolate avocado mousse that is both a healthy dessert and a satisfying treat for any occasion. This easy, no-bake recipe combines rich chocolate flavor with the goodness of avocado, making it a delightful vegan chocolate option. Enjoy this luxurious dessert that will impress your guests and keep your cravings in check without sacrificing taste.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>chocolate mousse, avocado dessert, healthy dessert, no-bake recipe, vegan chocolate, easy recipe</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Chocolate Avocado Mousse</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Indulge in a rich Chocolate Avocado Mousse that's healthy and delicious! Perfect for dessert lovers seeking guilt-free treats.</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_5.jpg</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-chocolate-avocado-mousse-recipe/</t>
         </is>
       </c>
     </row>
@@ -1602,6 +2486,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523175/bd6c2671949.png</t>
@@ -1630,6 +2515,186 @@
       <c r="S7" t="inlineStr">
         <is>
           <t>DONE</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Viral Sweet Treat Everyone Loves
+## Introduction
+The allure of a delicious dessert is hard to resist, and this viral sweet treat brings joy to every occasion. With rich cocoa flavor that wraps around a buttery texture, this dessert creates a harmony of indulgence with delightful bursts of chocolate and fun rainbow sprinkles. Ideal for dessert lovers of all ages, every bite is sure to elicit smiles and satisfaction. 
+This recipe perfects the balance between sweet and rich, aromatic nuances of vanilla, and the pleasing crunch of sprinkles. Sweetened with a generous scoop of granulated sugar and a rich dose of chocolate chips, this treat does not shy away from flavors and textures. Whether you're planning a party, a family gathering, or simply want to indulge in something delightful, this dessert is just the ticket. The visual appeal of vibrant sprinkles atop chocolate squares also makes it a feast for the eyes.
+Moreover, its ease of preparation means that even novice bakers can whip this up in a flash. In just under an hour, you can create a dessert that looks stunning and tastes divine. When served warm or at room temperature, this sweet treat can be enjoyed on various occasions, from birthdays to casual get-togethers or even as a sweet end to a cozy family dinner.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 30 minutes
+- Total Time: 40 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 16
+- Calories: ~210 per serving
+## Ingredients
+The success of this dessert relies on the perfect combination of ingredients. Here’s what you’ll need:
+- 1 cup all-purpose flour
+- 1 cup granulated sugar
+- 1/2 cup unsweetened cocoa powder
+- 1/2 cup butter, melted
+- 2 large eggs
+- 1 teaspoon vanilla extract
+- 1/2 teaspoon baking powder
+- 1/4 teaspoon salt
+- 1 cup chocolate chips
+- 1/2 cup rainbow sprinkles
+{{image_ing_1}}
+## Instructions
+Understanding each step is essential for perfecting the dessert.
+### Preheating and Preparing
+1. Preheat your oven to 350°F (175°C) to create the ideal baking environment for your treat.
+2. Grease a 9x9 inch baking dish effectively to ensure easy removal of the squares after they are baked.
+### Mixing Dry Ingredients
+3. In a large mixing bowl, combine the flour, granulated sugar, unsweetened cocoa powder, baking powder, and salt. This dry mix sets the foundation for a beautifully fluffy and rich texture.
+4. Whisking these ingredients together ensures an even distribution of flavors, reducing the possibility of clumping.
+### Mixing Wet Ingredients
+5. In a separate bowl, whisk together the melted butter, large eggs, and vanilla extract until smooth. Mixing these ingredients thoroughly adds not only richness but also moisture to the final dish.
+6. This step is crucial as it allows the eggs to incorporate air into the batter, helping the dessert rise as it bakes.
+### Combining Ingredients
+7. Carefully pour the wet ingredient mixture into the dry ingredients, mixing just until combined to avoid overmixing, which can lead to a dense final product.
+8. Gently fold in the chocolate chips and half of the rainbow sprinkles, making sure they are evenly distributed for delightful surprise bites throughout the dessert.
+### Filling the Baking Dish
+9. Spread the batter evenly in the prepared 9x9 inch baking dish, ensuring a level surface for even baking.
+10. Tapping the dish gently helps settle the batter and prevents air bubbles from forming, ensuring each square bakes to perfection.
+### Baking Process
+11. Place the baking dish in the preheated oven and bake for 25-30 minutes. Keep an eye on the baking time; shorter may lead to undercooked centers, while longer can dry out the edges.
+12. To check for doneness, insert a toothpick into the center of the dessert. It should come out clean if the baking is just right. 
+### Cooling Down
+13. Once baked, let the squares cool completely in the baking dish before cutting. Allowing them to cool will prevent them from crumbling when sliced.
+14. Patience is key here as the cooling process allows flavors to meld and develop perfectly.
+### Garnishing for Presentation
+15. Top the cooled dessert with the remaining rainbow sprinkles for that perfect finishing touch. The sprinkles add an appealing burst of color and a fun texture, elevating the overall presentation of your culinary creation.
+This viral sweet treat is a wonderful expression of skill and simplicity, exuding irresistible charm from every angle. As you master each step, you'll not only enjoy the creation process but also delight in sharing this delightful dessert with family and friends.
+## Serving Suggestions
+Enhancing the experience of serving the dessert can elevate your gathering. Thoughtful presentation and complementary sides can turn a tasty treat into a memorable moment.
+### Ideal Accompaniments
+To create a well-rounded dessert experience, consider pairing your squares with delicious accompaniments. 
+- **Vanilla Ice Cream:** Serving with a scoop of creamy vanilla ice cream adds a delightful contrast to the rich chocolate squares, balancing the flavors and temperatures beautifully. The ice cream melts slightly on the warm brownies, creating a velvety sauce that enhances every bite.
+- **Fresh Fruits:** Pairing the dessert with fresh fruits like strawberries or raspberries introduces a refreshing contrast to the rich chocolate flavor. The natural acidity of the fruits cuts through the sweetness, providing a refreshing finish.
+### Creative Plating Ideas
+Elevating the visual appeal of your dessert can impress your guests and enhance the overall enjoyment. Here are some plating suggestions:
+- **Colorful Plates:** Present the squares on colorful dessert plates that complement the vibrant hues of the rainbow sprinkles. This adds an exciting visual element that makes the dessert pop.
+- **Powdered Sugar Dusting:** A light sprinkle of powdered sugar over the top of the squares not only adds a touch of elegance but also gives an extra hint of sweetness.
+- **Artistic Chocolate Drizzle:** Drizzling chocolate sauce artistically around the plate creates a gourmet touch. Use a squeeze bottle or a spoon to create beautiful designs that will impress.
+## Nutritional Information
+Understanding the nutritional aspect can aid in mindful eating. While desserts are often seen as indulgences, grasping their content can help you enjoy them more responsibly.
+### Caloric Breakdown
+Each serving contains approximately 210 calories, making it a moderate indulgence. This relatively low calorie count allows for enjoyment without excessive guilt. 
+- **Portion Control:** For those mindful of calorie intake, moderation is key. Devilishly delicious yet fairly manageable, these dessert squares can easily fit into various dietary preferences with careful portion choices.
+### Key Nutrients
+Every dessert brings something to the table, and this one is no different.
+- **Carbohydrates:** The dessert incorporates carbohydrates mainly from sugar and flour, contributing to the energy boost you may expect from a sweet dish. 
+- **Fats:** Butter and chocolate chips introduce necessary fats, which help in creating a deliciously moist texture.
+- **Proteins:** Eggs it a notable protein source, adding to the overall nutritional profile of the treat.
+## Tips for Success
+Perfecting your dessert takes a little extra knowledge, so keep these tips in mind to achieve optimal results.
+### Ingredient Substitutions
+Baking allows for creativity, and there are ways to swap ingredients for personal preferences or dietary needs.
+- **Healthier Options:** For a healthier version of this treat, consider using applesauce instead of butter. This will reduce fat content while still maintaining moisture.
+- **Whole Wheat Flour:** Substituting whole wheat flour adds a nuttier flavor and incorporates more fiber into the dessert, making it a bit more wholesome.
+### Storage Tips
+To ensure your dessert stays fresh for longer, consider these storage strategies.
+- **Airtight Storage:** Store any leftovers in an airtight container at room temperature for up to three days. This helps maintain the texture and moisture of the dessert.
+- **Refrigeration:** For longer freshness, refrigerate the dessert, but it’s advisable to allow it to come to room temperature before serving to preserve its best flavors and textures.
+## Variations of the Recipe
+Experimenting with variations can add a personal twist to the classic recipe. With a few modifications, you can create an entirely new experience.
+### Flavor Enhancements
+Adding unique elements to the batter can provide a delightful surprise.
+- **Citrus Zest:** Infusing your batter with orange zest or a splash of almond extract can create unique flavor profiles that complement the chocolate beautifully.
+- **Nuts:** Adding nuts such as walnuts or pecans will introduce crunchy elements to your dessert, giving it a delightful texture contrast against the soft squares.
+### Seasonal Themes
+Baking is an excellent opportunity to celebrate various occasions through themed variations.
+- **Festive Sprinkles:** Incorporate holiday-themed sprinkles or toppings for celebrations. Themed sprinkles can add a cheerful touch and connect the dessert to the festive spirit.
+- **Peppermint Treats:** During winter holidays, consider adding peppermint chunks or crushed candy canes to the batter for a seasonal twist that brings warmth and comfort to your dessert selection.
+## Common Mistakes to Avoid
+Being aware of pitfalls can save time and frustration during preparation. Here are common errors to watch out for when attempting this dessert.
+### Overmixing the Batter
+A common mistake in baking is overmixing, which can lead to an undesirable texture.
+- **Mix Until Just Combined:** Ensure to mix the ingredients until they are just combined. Overmixing can lead to a dense and chewy texture instead of the intended fudgy finish.
+### Incorrect Baking Time
+Timing is critical when baking; being diligent in monitoring the clock can make all the difference.
+- **Baking Time Awareness:** Keep a close eye on the baking time to avoid over-baking. While a toothpick check is a dependable method, regular monitoring will help to establish optimal doneness, preventing dry treat squares.
+## Conclusion
+This viral sweet treat is a delightful combination of chocolatey goodness and fun sprinkles, perfect for any dessert lover. With a preparation time of just 10 minutes and a total cooking time of 40 minutes, you'll have a delicious dessert bursting with flavor and texture ready to serve. Each piece offers a balance of indulgence and cheer that can bring joy to any occasion.
+</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viral Sweet Treat Everyone Loves</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Choco-Sprinkle Brownie Bites: Easy and Delicious Sweet Treat Recipe</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Chocolate Chip Rainbow Bliss Bars</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Indulge in these delightful Choco-Sprinkle Brownie Bites, the perfect sweet treat for any occasion. This easy dessert recipe combines rich chocolate chips with colorful rainbow sprinkles, making it a fun and festive addition to your baking repertoire. Whether for a party or a cozy evening at home, these brownie bites are sure to bring joy to every bite.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>sweet treat, dessert recipe, chocolate chips, rainbow sprinkles, baking, easy recipe</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Viral Chocolate Chip Brownies</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Indulge in this viral sweet treat everyone loves! Easy to make and perfect for any occasion, it’s a chocolate lover's dream!</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_6.jpg</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/viral-sweet-treat-everyone-loves/</t>
         </is>
       </c>
     </row>
@@ -1788,6 +2853,7 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0523175/dedbe9a194c.png</t>
@@ -1818,6 +2884,163 @@
           <t>DONE</t>
         </is>
       </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>DONE ARTICLE</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Easy Viral Chocolate Lava Mug Cake Recipe
+## Introduction
+The allure of a warm, gooey dessert in just minutes is hard to resist. This Viral Chocolate Lava Mug Cake epitomizes quick and delightful indulgence. Within mere moments, you'll experience the joy of a chocolate confection that oozes rich flavor, making it a popular choice for those craving a sweet treat without the hassle of extensive baking. Whether it's a late-night snack, a quick dessert after dinner, or an unexpected guest who needs dessert in a pinch, this recipe fits any occasion seamlessly.
+Imagine the aroma of chocolate wafting through your kitchen as you prepare this delightful treat. With only a few ingredients, it offers both simplicity and satisfaction. The unique combination of a fluffy mug cake and a molten chocolate center gives this dessert its signature style. It’s a perfect meal-ending experience for anyone who loves chocolate—quickly made and easily enjoyed right from the mug. 
+## Recipe Overview
+- Prep Time: 5 minutes
+- Cook Time: 1 minute
+- Total Time: 6 minutes
+- Course: Dessert
+- Cuisine: American
+- Servings: 1
+- Calories: ~350 per serving
+This Chocolate Lava Mug Cake is not only easy to whip up, but it's also designed to cater to single serving needs, making it perfect for a quick dessert fix. With a total time of just 6 minutes, this dessert brings together simple ingredients to create a decadent masterpiece. In a matter of minutes, you can enjoy a warm treat that feels extravagant yet is incredibly straightforward to prepare. Perfect for everyone from busy parents to college students, it’s a treat that doesn’t require an oven and eliminates the mess of traditional baking techniques.
+## Ingredients
+The rich taste of this dessert comes from a blend of everyday ingredients, easily found in most kitchens. Here, we break down each component for your Chocolate Lava Mug Cake.
+### Essential Dry Ingredients
+- All-purpose flour
+- Granulated sugar
+- Unsweetened cocoa powder
+- Baking powder
+### Essential Wet Ingredients
+- Milk
+- Vegetable oil
+- Vanilla extract
+### The Star Ingredient
+- Chocolate square (about 1 ounce), or chocolate chips for added texture
+### Optional Toppings
+- Ice cream
+- Whipped cream
+This simple ingredient list is all you need to create the indulgent experience of a chocolate lava cake in a minute. The dry ingredients mix harmoniously to form the cake base, while the addition of milk, oil, and vanilla adds moisture and flavor to create a tender, delectable cake. The chocolate square or chips become the centerpiece of this treat, transforming the cake into a warm, molten delight as it melts during cooking. If you wish to elevate the experience even further, adding a scoop of ice cream or a dollop of whipped cream can provide a refreshing contrast to the warm chocolate.
+{{image_ing_1}}
+## Instructions
+Crafting this delightful dessert involves a few straightforward steps that render efficient results.
+1. In a microwave-safe mug, combine the flour, sugar, cocoa powder, and baking powder. Mix well.
+2. Add the milk, vegetable oil, and vanilla extract to the dry ingredients. Stir until smooth.
+3. Push the chocolate square into the center of the batter, making sure it is covered by the mixture.
+4. Microwave the mug on high for 40-60 seconds, watching closely to avoid overflow.
+5. Allow the mug cake to cool for a minute before serving.
+6. Optionally, top with a scoop of ice cream or whipped cream for an extra treat.
+7. Enjoy your decadent dessert right from the mug!
+### Combining Dry Ingredients
+Begin by gathering your dry ingredients and mixing them thoroughly to ensure an even distribution of flavors. This step is important as it helps prevent clumping, ensuring that each bite of the mug cake is uniformly delicious. 
+### Mixing Wet Ingredients
+After the dry mix, combine the wet elements to bring moisture and additional flavor to the cake batter. The milk, vegetable oil, and vanilla extract provide not just moisture but also an enriching aroma and taste that elevates the overall dessert experience. Stirring until smooth guarantees that all ingredients combine seamlessly.
+### Assembling the Mug Cake
+Push the chocolate square into the center of the batter; this step is crucial for achieving that famous lava effect. This chocolate square will melt during the cooking process, forming the indulgent center that contrasts beautifully with the fluffy outer cake.
+### Microwaving the Mug Cake
+Microwave the concoction while remaining vigilant about timing to avoid a messy overflow. Microwaving for 40-60 seconds is ideal; watching closely will help you gauge when it’s time to stop the cooking process just before the cake may overflow or overcook.
+### Cooling and Serving
+Let the mug cake cool slightly before indulging in its rich goodness, perhaps topped with a scoop of ice cream or whipped cream. This cooling step allows the steam to dissipate, ensuring that the lava effect remains intact and does not turn into a soupy mess. Toppings are an optional gem that can transform this simple mug cake into a gourmet experience deserving of any dinner table.
+### Ideal Timing Tips
+When creating the Viral Chocolate Lava Mug Cake, precision in timing is key to achieving the ideal texture. Watching your microwave closely during cooking is essential to prevent overcooking the cake. The perfect mug cake should have set edges while retaining a delightfully gooey center that creates the signature lava effect. If you wish to experiment, start checking the cake after 40 seconds in the microwave, allowing yourself to gauge how quickly your appliance cooks. Different microwaves can have varied wattages, affecting cooking time, so it may require a couple of tries to perfect the timing for your specific model.
+## Serving Suggestions
+This dessert can be enjoyed plain or dressed up for special occasions. It’s an incredibly versatile treat that caters to both casual and festive gatherings.
+### Basic Serving
+For a relaxed and indulgent experience, serve the cake directly from the mug. This approach not only minimizes cleanup but also maintains the cake's warmth and appeal. Embrace the rustic charm of digging in with a spoon, which adds to the delight of this satisfying dessert.
+### Enhanced Presentation
+To elevate the presentation, consider adding a scoop of ice cream or a dollop of whipped cream on top of the mug cake. A scoop of vanilla ice cream complements the rich chocolate flavor while adding a delightful contrast in temperature and texture. Drizzling some chocolate sauce or caramel over the top can further enhance both the flavor and aesthetics of the dish, turning a simple mug cake into a beautiful dessert to impress guests or delight yourself during a self-care evening.
+## Nutritional Information
+For those mindful of what they consume, here's a brief overview of the nutritional makeup of the cake.
+### Caloric Content
+Each serving of the Viral Chocolate Lava Mug Cake contains approximately 350 calories. This calorie count is reasonable, especially as it fits within the enjoyment of an occasional sweet treat, keeping indulgence in moderation.
+### Nutritional Benefits
+While indulgent, there are aspects of this dessert that can be beneficial. Cocoa is known for its rich antioxidant properties, which may contribute to health when consumed in moderation. So, while this cake is certainly a dessert, it can be enjoyed not just for its taste but also for a touch of nutritional goodness.
+## Variations of the Mug Cake
+Explore different twists on the classic chocolate lava mug cake to suit your taste preferences. This versatility opens doors to personalized creations tailored to different occasions or cravings.
+### Flavor Enhancements
+Consider incorporating a pinch of cinnamon or espresso powder into the batter. These additions can introduce a deeper flavor profile that complements the chocolate. Spice lovers might enjoy the subtle warmth of cinnamon, while coffee enthusiasts may appreciate the complexity that espresso adds to the cake.
+### Ingredient Swaps
+If you’re considering alternatives to the standard ingredients, try using almond milk or coconut oil. These substitutions can cater to various dietary needs or preferences. Almond milk provides a lighter taste, while coconut oil can add a delightful coconut aroma and flavor to the cake.
+### Chocolate Choices
+The harmonious chocolate center can be adjusted according to personal preference. Opt for dark chocolate for a more pronounced cocoa flavor or white chocolate for a sweeter taste. For adventurous palates, experimenting with Nutella could bring an entirely new texture and flavor profile to the dessert. The flexibility in chocolate choice makes this recipe highly adaptable to suit any chocolate lover.
+## Common Mistakes to Avoid
+Being aware of common pitfalls in mug cake preparation can help ensure a delightful outcome.
+### Overmixing Batter
+A common error is overmixing the batter once the wet ingredients are added. Overmixing could result in a denser texture, reducing the cake's desirable lightness. Mix just enough to combine the ingredients until smooth but avoid excessive stirring.
+### Incorrect Microwave Timing
+Incorrect timing is another frequent mistake. Be cautious in monitoring the cooking time; the ideal mug cake should rise slightly but still remain soft in the center. If in doubt, it's better to undercook slightly, as you can always return it to the microwave for a few additional seconds.
+### Ignoring Cooling Time
+Don't skip the cooling period. Allowing the cake to sit in the mug for a minute after microwaving is crucial, as it continues to cook slightly with residual heat. This cooling allows the cake to set properly and enhances both flavor and texture.
+## Storage Options
+While best enjoyed fresh, many may wonder how to store any leftovers from this single-serving cake.
+### Refrigeration
+If any cake remains, you can seal the mug and refrigerate it. It's best consumed within a day or two to fully enjoy its intended texture and flavor. Storing it too long may lead to a drier cake, as the moisture will dissipate.
+### Reheating
+When you’re ready to indulge again, reheat the mug cake in the microwave for a few seconds to return its gooey texture. Be cautious not to overheat, as this can lead to a rubbery consistency, losing the delightful lava element that makes this cake so irresistible.
+## Conclusion
+The Viral Chocolate Lava Mug Cake presents a beautifully simple yet indulgent dessert option that captures the essence of comfort food. With just six minutes from start to finish, it stands out as a convenient treat suitable for any occasion. Whether enjoyed straight from the mug or garnished with delightful toppings, this dessert is sure to be a crowd-pleaser that brings joy with every bite.
+</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Easy Viral Chocolate Lava Mug Cake Recipe</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Easy Chocolate Lava Mug Cake Recipe in 6 Minutes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Decadent Chocolate Lava Mug Cake</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Indulge in a rich chocolate experience with this easy chocolate lava mug cake recipe, perfect for satisfying your dessert cravings in just 6 minutes. Made in the microwave, this quick recipe delivers a warm, gooey center that melts in your mouth, making it an ideal treat for cozy nights in. Enjoy the simple pleasure of homemade lava cake without the fuss and impress your loved ones with this delightful dessert.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>chocolate, mug cake, dessert, quick recipe, microwave, lava cake</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Chocolate Lava Mug Cake</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>Indulge in a Viral Chocolate Lava Mug Cake that's ready in just 6 minutes! A delicious, gooey treat for everyone! 🍫🔥</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>on</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Low Carb Snacks &amp; Desserts</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_7.jpg</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -3039,8 +3039,16 @@
           <t>/Users/elmehdierraji/Documents/GitHub/pt-rest/ALL/A2-Pinterest_02-out/output_images/image_7.jpg</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>https://lowcarbdaily.com/easy-viral-chocolate-lava-mug-cake-recipe/</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ALL/A2-Pinterest_02-out/Recipes.xlsx
+++ b/ALL/A2-Pinterest_02-out/Recipes.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
